--- a/Camaras/Camaras_unificado_v3.1_ALBALI_actualizado.xlsx
+++ b/Camaras/Camaras_unificado_v3.1_ALBALI_actualizado.xlsx
@@ -899,11 +899,7 @@
           <t>PS 325,1 a</t>
         </is>
       </c>
-      <c r="N2" s="15" t="inlineStr">
-        <is>
-          <t>325113</t>
-        </is>
-      </c>
+      <c r="N2" s="15" t="n"/>
       <c r="O2" s="15" t="inlineStr">
         <is>
           <t>CÁMARA FIJA IP</t>
@@ -1046,11 +1042,7 @@
           <t>ATI 312.4</t>
         </is>
       </c>
-      <c r="N3" s="15" t="inlineStr">
-        <is>
-          <t>387772</t>
-        </is>
-      </c>
+      <c r="N3" s="15" t="n"/>
       <c r="O3" s="15" t="inlineStr">
         <is>
           <t>CÁMARA FIJA IP</t>
@@ -1193,11 +1185,7 @@
           <t>ATI 321.2</t>
         </is>
       </c>
-      <c r="N4" s="15" t="inlineStr">
-        <is>
-          <t>420421</t>
-        </is>
-      </c>
+      <c r="N4" s="15" t="n"/>
       <c r="O4" s="15" t="inlineStr">
         <is>
           <t>CÁMARA FIJA IP</t>
@@ -1340,11 +1328,7 @@
           <t>PS 342,7 a</t>
         </is>
       </c>
-      <c r="N5" s="15" t="inlineStr">
-        <is>
-          <t>342773</t>
-        </is>
-      </c>
+      <c r="N5" s="15" t="n"/>
       <c r="O5" s="15" t="inlineStr">
         <is>
           <t>CÁMARA FIJA IP</t>
@@ -1487,11 +1471,7 @@
           <t>ATI 321.2</t>
         </is>
       </c>
-      <c r="N6" s="15" t="inlineStr">
-        <is>
-          <t>420421</t>
-        </is>
-      </c>
+      <c r="N6" s="15" t="n"/>
       <c r="O6" s="15" t="inlineStr">
         <is>
           <t>CÁMARA FIJA IP</t>
@@ -1634,11 +1614,7 @@
           <t>PS 344,9 a</t>
         </is>
       </c>
-      <c r="N7" s="15" t="inlineStr">
-        <is>
-          <t>344986</t>
-        </is>
-      </c>
+      <c r="N7" s="15" t="n"/>
       <c r="O7" s="15" t="inlineStr">
         <is>
           <t>CÁMARA FIJA IP</t>
@@ -1781,11 +1757,7 @@
           <t>TÚNEL DE LA SIERRA DE LAS ÁGUILAS (1.227m) (boca Albacete</t>
         </is>
       </c>
-      <c r="N8" s="15" t="inlineStr">
-        <is>
-          <t>470962</t>
-        </is>
-      </c>
+      <c r="N8" s="15" t="n"/>
       <c r="O8" s="15" t="inlineStr">
         <is>
           <t>CÁMARA FIJA IP</t>
@@ -1928,11 +1900,7 @@
           <t>PS 350,6 a</t>
         </is>
       </c>
-      <c r="N9" s="15" t="inlineStr">
-        <is>
-          <t>350643</t>
-        </is>
-      </c>
+      <c r="N9" s="15" t="n"/>
       <c r="O9" s="15" t="inlineStr">
         <is>
           <t>CÁMARA FIJA IP</t>
@@ -2075,11 +2043,7 @@
           <t>VIADUCTO - SCVL-14A (BTS08A)</t>
         </is>
       </c>
-      <c r="N10" s="15" t="inlineStr">
-        <is>
-          <t>382592</t>
-        </is>
-      </c>
+      <c r="N10" s="15" t="n"/>
       <c r="O10" s="15" t="inlineStr">
         <is>
           <t>CÁMARA FIJA IP</t>
@@ -2222,11 +2186,7 @@
           <t>ATI 312.4</t>
         </is>
       </c>
-      <c r="N11" s="15" t="inlineStr">
-        <is>
-          <t>387772</t>
-        </is>
-      </c>
+      <c r="N11" s="15" t="n"/>
       <c r="O11" s="15" t="inlineStr">
         <is>
           <t>CÁMARA FIJA IP</t>
@@ -2369,11 +2329,7 @@
           <t>ATF 321.1</t>
         </is>
       </c>
-      <c r="N12" s="15" t="inlineStr">
-        <is>
-          <t>405999</t>
-        </is>
-      </c>
+      <c r="N12" s="15" t="n"/>
       <c r="O12" s="15" t="inlineStr">
         <is>
           <t>CÁMARA FIJA IP</t>
@@ -2516,11 +2472,7 @@
           <t>PS 368,9 a</t>
         </is>
       </c>
-      <c r="N13" s="15" t="inlineStr">
-        <is>
-          <t>368928</t>
-        </is>
-      </c>
+      <c r="N13" s="15" t="n"/>
       <c r="O13" s="15" t="inlineStr">
         <is>
           <t>CÁMARA FIJA IP</t>
@@ -2663,11 +2615,7 @@
           <t>PB Las Chozas</t>
         </is>
       </c>
-      <c r="N14" s="15" t="inlineStr">
-        <is>
-          <t>407496</t>
-        </is>
-      </c>
+      <c r="N14" s="15" t="n"/>
       <c r="O14" s="15" t="inlineStr">
         <is>
           <t>CÁMARA FIJA IP</t>
@@ -2810,11 +2758,7 @@
           <t>VIADUCTO SOBRE EL CORDEL DEL CAMINO DE SAX - SCVL-21</t>
         </is>
       </c>
-      <c r="N15" s="15" t="inlineStr">
-        <is>
-          <t>436290</t>
-        </is>
-      </c>
+      <c r="N15" s="15" t="n"/>
       <c r="O15" s="15" t="inlineStr">
         <is>
           <t>CÁMARA FIJA IP</t>
@@ -2957,11 +2901,7 @@
           <t>PS 364,8 a</t>
         </is>
       </c>
-      <c r="N16" s="15" t="inlineStr">
-        <is>
-          <t>364859</t>
-        </is>
-      </c>
+      <c r="N16" s="15" t="n"/>
       <c r="O16" s="15" t="inlineStr">
         <is>
           <t>CÁMARA FIJA IP</t>
@@ -3104,11 +3044,7 @@
           <t>PS 338,6 a</t>
         </is>
       </c>
-      <c r="N17" s="15" t="inlineStr">
-        <is>
-          <t>338690</t>
-        </is>
-      </c>
+      <c r="N17" s="15" t="n"/>
       <c r="O17" s="15" t="inlineStr">
         <is>
           <t>CÁMARA FIJA IP</t>
@@ -3251,11 +3187,7 @@
           <t>ATI 312.3</t>
         </is>
       </c>
-      <c r="N18" s="15" t="inlineStr">
-        <is>
-          <t>365625</t>
-        </is>
-      </c>
+      <c r="N18" s="15" t="n"/>
       <c r="O18" s="15" t="inlineStr">
         <is>
           <t>CÁMARA FIJA IP</t>
@@ -3398,11 +3330,7 @@
           <t>PS 433,7 a</t>
         </is>
       </c>
-      <c r="N19" s="15" t="inlineStr">
-        <is>
-          <t>433784</t>
-        </is>
-      </c>
+      <c r="N19" s="15" t="n"/>
       <c r="O19" s="15" t="inlineStr">
         <is>
           <t>CÁMARA FIJA IP</t>
@@ -3545,11 +3473,7 @@
           <t>PS 434,5 a</t>
         </is>
       </c>
-      <c r="N20" s="15" t="inlineStr">
-        <is>
-          <t>434581</t>
-        </is>
-      </c>
+      <c r="N20" s="15" t="n"/>
       <c r="O20" s="15" t="inlineStr">
         <is>
           <t>CÁMARA FIJA IP</t>
@@ -3692,11 +3616,7 @@
           <t>ATI 321.5</t>
         </is>
       </c>
-      <c r="N21" s="15" t="inlineStr">
-        <is>
-          <t>460006</t>
-        </is>
-      </c>
+      <c r="N21" s="15" t="n"/>
       <c r="O21" s="15" t="inlineStr">
         <is>
           <t>CÁMARA FIJA IP</t>
@@ -3839,11 +3759,7 @@
           <t>PS 374,7 a</t>
         </is>
       </c>
-      <c r="N22" s="15" t="inlineStr">
-        <is>
-          <t>374717</t>
-        </is>
-      </c>
+      <c r="N22" s="15" t="n"/>
       <c r="O22" s="15" t="inlineStr">
         <is>
           <t>CÁMARA FIJA IP</t>
@@ -3986,11 +3902,7 @@
           <t>ATI 321.2</t>
         </is>
       </c>
-      <c r="N23" s="15" t="inlineStr">
-        <is>
-          <t>420421</t>
-        </is>
-      </c>
+      <c r="N23" s="15" t="n"/>
       <c r="O23" s="15" t="inlineStr">
         <is>
           <t>CÁMARA FIJA IP</t>
@@ -4133,11 +4045,7 @@
           <t>ATF 312.1</t>
         </is>
       </c>
-      <c r="N24" s="15" t="inlineStr">
-        <is>
-          <t>342890</t>
-        </is>
-      </c>
+      <c r="N24" s="15" t="n"/>
       <c r="O24" s="15" t="inlineStr">
         <is>
           <t>CÁMARA FIJA IP</t>
@@ -4280,11 +4188,7 @@
           <t>PS 430,1 a</t>
         </is>
       </c>
-      <c r="N25" s="15" t="inlineStr">
-        <is>
-          <t>430117</t>
-        </is>
-      </c>
+      <c r="N25" s="15" t="n"/>
       <c r="O25" s="15" t="inlineStr">
         <is>
           <t>CÁMARA FIJA IP</t>
@@ -4427,11 +4331,7 @@
           <t>PS 463,0a (PS 462,9 a)</t>
         </is>
       </c>
-      <c r="N26" s="15" t="inlineStr">
-        <is>
-          <t>463016</t>
-        </is>
-      </c>
+      <c r="N26" s="15" t="n"/>
       <c r="O26" s="15" t="inlineStr">
         <is>
           <t>CÁMARA FIJA IP</t>
@@ -4574,11 +4474,7 @@
           <t>PCA Hoya Gonzalo</t>
         </is>
       </c>
-      <c r="N27" s="15" t="inlineStr">
-        <is>
-          <t>348862</t>
-        </is>
-      </c>
+      <c r="N27" s="15" t="n"/>
       <c r="O27" s="15" t="inlineStr">
         <is>
           <t>CÁMARA FIJA IP</t>
@@ -4721,11 +4617,7 @@
           <t>PS 332,8 a</t>
         </is>
       </c>
-      <c r="N28" s="15" t="inlineStr">
-        <is>
-          <t>332851</t>
-        </is>
-      </c>
+      <c r="N28" s="15" t="n"/>
       <c r="O28" s="15" t="inlineStr">
         <is>
           <t>CÁMARA FIJA IP</t>
@@ -4868,11 +4760,7 @@
           <t>ET PAET Chinchilla AV</t>
         </is>
       </c>
-      <c r="N29" s="15" t="inlineStr">
-        <is>
-          <t>336566</t>
-        </is>
-      </c>
+      <c r="N29" s="15" t="n"/>
       <c r="O29" s="15" t="inlineStr">
         <is>
           <t>CÁMARA FIJA IP</t>
@@ -5015,11 +4903,7 @@
           <t>PCA Atalaya</t>
         </is>
       </c>
-      <c r="N30" s="15" t="inlineStr">
-        <is>
-          <t>395700</t>
-        </is>
-      </c>
+      <c r="N30" s="15" t="n"/>
       <c r="O30" s="15" t="inlineStr">
         <is>
           <t>CÁMARA FIJA IP</t>
@@ -5162,11 +5046,7 @@
           <t>Bifurcación Murcia</t>
         </is>
       </c>
-      <c r="N31" s="15" t="inlineStr">
-        <is>
-          <t>461719</t>
-        </is>
-      </c>
+      <c r="N31" s="15" t="n"/>
       <c r="O31" s="15" t="inlineStr">
         <is>
           <t>CÁMARA FIJA IP</t>
@@ -5396,11 +5276,7 @@
           <t>ATI 321.5</t>
         </is>
       </c>
-      <c r="N33" s="15" t="inlineStr">
-        <is>
-          <t>460006</t>
-        </is>
-      </c>
+      <c r="N33" s="15" t="n"/>
       <c r="O33" s="15" t="inlineStr">
         <is>
           <t>CÁMARA FIJA IP</t>
@@ -5543,11 +5419,7 @@
           <t>PS 338,6 a</t>
         </is>
       </c>
-      <c r="N34" s="15" t="inlineStr">
-        <is>
-          <t>338690</t>
-        </is>
-      </c>
+      <c r="N34" s="15" t="n"/>
       <c r="O34" s="15" t="inlineStr">
         <is>
           <t>CÁMARA FIJA IP</t>
@@ -5690,11 +5562,7 @@
           <t>SE 312 - SUBESTACIÓN ELÉCTRICA CAMPANARIO</t>
         </is>
       </c>
-      <c r="N35" s="15" t="inlineStr">
-        <is>
-          <t>378076</t>
-        </is>
-      </c>
+      <c r="N35" s="15" t="n"/>
       <c r="O35" s="15" t="inlineStr">
         <is>
           <t>CÁMARA FIJA IP</t>
@@ -5837,11 +5705,7 @@
           <t>PS 434,5 a</t>
         </is>
       </c>
-      <c r="N36" s="15" t="inlineStr">
-        <is>
-          <t>434581</t>
-        </is>
-      </c>
+      <c r="N36" s="15" t="n"/>
       <c r="O36" s="15" t="inlineStr">
         <is>
           <t>CÁMARA FIJA IP</t>
@@ -5984,11 +5848,7 @@
           <t>PS 376,0 a</t>
         </is>
       </c>
-      <c r="N37" s="15" t="inlineStr">
-        <is>
-          <t>376072</t>
-        </is>
-      </c>
+      <c r="N37" s="15" t="n"/>
       <c r="O37" s="15" t="inlineStr">
         <is>
           <t>CÁMARA FIJA IP</t>
@@ -6131,11 +5991,7 @@
           <t>Estación Villena</t>
         </is>
       </c>
-      <c r="N38" s="15" t="inlineStr">
-        <is>
-          <t>435487</t>
-        </is>
-      </c>
+      <c r="N38" s="15" t="n"/>
       <c r="O38" s="15" t="inlineStr">
         <is>
           <t>CÁMARA FIJA IP</t>
@@ -6278,11 +6134,7 @@
           <t>PR 483,7 a (Pérgola Ramal de Mercancías)</t>
         </is>
       </c>
-      <c r="N39" s="15" t="inlineStr">
-        <is>
-          <t>483753</t>
-        </is>
-      </c>
+      <c r="N39" s="15" t="n"/>
       <c r="O39" s="15" t="inlineStr">
         <is>
           <t>CÁMARA FIJA IP</t>
@@ -6425,11 +6277,7 @@
           <t>PS 347,5 a</t>
         </is>
       </c>
-      <c r="N40" s="15" t="inlineStr">
-        <is>
-          <t>347517</t>
-        </is>
-      </c>
+      <c r="N40" s="15" t="n"/>
       <c r="O40" s="15" t="inlineStr">
         <is>
           <t>CÁMARA FIJA IP</t>
@@ -6572,11 +6420,7 @@
           <t>Estación Villena</t>
         </is>
       </c>
-      <c r="N41" s="15" t="inlineStr">
-        <is>
-          <t>435487</t>
-        </is>
-      </c>
+      <c r="N41" s="15" t="n"/>
       <c r="O41" s="15" t="inlineStr">
         <is>
           <t>CÁMARA FIJA IP</t>
@@ -6719,11 +6563,7 @@
           <t>SE 312 - SUBESTACIÓN ELÉCTRICA CAMPANARIO</t>
         </is>
       </c>
-      <c r="N42" s="15" t="inlineStr">
-        <is>
-          <t>378076</t>
-        </is>
-      </c>
+      <c r="N42" s="15" t="n"/>
       <c r="O42" s="15" t="inlineStr">
         <is>
           <t>CÁMARA FIJA IP</t>
@@ -6866,11 +6706,7 @@
           <t>PCA El Mugrón</t>
         </is>
       </c>
-      <c r="N43" s="15" t="inlineStr">
-        <is>
-          <t>384772</t>
-        </is>
-      </c>
+      <c r="N43" s="15" t="n"/>
       <c r="O43" s="15" t="inlineStr">
         <is>
           <t>CÁMARA FIJA IP</t>
@@ -7013,11 +6849,7 @@
           <t>TÚNEL DE LAS BARRANCADAS (2.856m) (boca Alicante)</t>
         </is>
       </c>
-      <c r="N44" s="15" t="inlineStr">
-        <is>
-          <t>444814</t>
-        </is>
-      </c>
+      <c r="N44" s="15" t="n"/>
       <c r="O44" s="15" t="inlineStr">
         <is>
           <t>CÁMARA FIJA IP</t>
@@ -7160,11 +6992,7 @@
           <t>PS 463,0a (PS 462,9 a)</t>
         </is>
       </c>
-      <c r="N45" s="15" t="inlineStr">
-        <is>
-          <t>463016</t>
-        </is>
-      </c>
+      <c r="N45" s="15" t="n"/>
       <c r="O45" s="15" t="inlineStr">
         <is>
           <t>CÁMARA FIJA IP</t>
@@ -7307,11 +7135,7 @@
           <t>Estación Villena</t>
         </is>
       </c>
-      <c r="N46" s="15" t="inlineStr">
-        <is>
-          <t>435487</t>
-        </is>
-      </c>
+      <c r="N46" s="15" t="n"/>
       <c r="O46" s="15" t="inlineStr">
         <is>
           <t>CÁMARA FIJA IP</t>
@@ -7454,11 +7278,7 @@
           <t>TÚNEL DE ACCESO ALICANTE (1.067m) (boca Albacete)</t>
         </is>
       </c>
-      <c r="N47" s="15" t="inlineStr">
-        <is>
-          <t>483956</t>
-        </is>
-      </c>
+      <c r="N47" s="15" t="n"/>
       <c r="O47" s="15" t="inlineStr">
         <is>
           <t>CÁMARA FIJA IP</t>
@@ -7601,11 +7421,7 @@
           <t>ATI 312.4</t>
         </is>
       </c>
-      <c r="N48" s="15" t="inlineStr">
-        <is>
-          <t>387772</t>
-        </is>
-      </c>
+      <c r="N48" s="15" t="n"/>
       <c r="O48" s="15" t="inlineStr">
         <is>
           <t>CÁMARA FIJA IP</t>
@@ -7748,11 +7564,7 @@
           <t>BASE DE MANTENIMIENTO MONFORTE DEL CID (NODO-9 GAR</t>
         </is>
       </c>
-      <c r="N49" s="15" t="inlineStr">
-        <is>
-          <t>465134</t>
-        </is>
-      </c>
+      <c r="N49" s="15" t="n"/>
       <c r="O49" s="15" t="inlineStr">
         <is>
           <t>CÁMARA FIJA IP</t>
@@ -7895,11 +7707,7 @@
           <t>ET PAET Villena AV</t>
         </is>
       </c>
-      <c r="N50" s="15" t="inlineStr">
-        <is>
-          <t>435487</t>
-        </is>
-      </c>
+      <c r="N50" s="15" t="n"/>
       <c r="O50" s="15" t="inlineStr">
         <is>
           <t>CÁMARA FIJA IP</t>
@@ -8042,11 +7850,7 @@
           <t>ATI 312.2</t>
         </is>
       </c>
-      <c r="N51" s="15" t="inlineStr">
-        <is>
-          <t>355696</t>
-        </is>
-      </c>
+      <c r="N51" s="15" t="n"/>
       <c r="O51" s="15" t="inlineStr">
         <is>
           <t>CÁMARA FIJA IP</t>
@@ -8189,11 +7993,7 @@
           <t>VIADUCTO SOBRE ACEQUIA DEL REY</t>
         </is>
       </c>
-      <c r="N52" s="15" t="inlineStr">
-        <is>
-          <t>431647</t>
-        </is>
-      </c>
+      <c r="N52" s="15" t="n"/>
       <c r="O52" s="15" t="inlineStr">
         <is>
           <t>CÁMARA FIJA IP</t>
@@ -8336,11 +8136,7 @@
           <t>VIADUCTO SOBRE A-35</t>
         </is>
       </c>
-      <c r="N53" s="15" t="inlineStr">
-        <is>
-          <t>405187</t>
-        </is>
-      </c>
+      <c r="N53" s="15" t="n"/>
       <c r="O53" s="15" t="inlineStr">
         <is>
           <t>CÁMARA FIJA IP</t>
@@ -8483,11 +8279,7 @@
           <t>PR 483,7 a (Pérgola Ramal de Mercancías)</t>
         </is>
       </c>
-      <c r="N54" s="15" t="inlineStr">
-        <is>
-          <t>483753</t>
-        </is>
-      </c>
+      <c r="N54" s="15" t="n"/>
       <c r="O54" s="15" t="inlineStr">
         <is>
           <t>CÁMARA FIJA IP</t>
@@ -8630,11 +8422,7 @@
           <t>ATI 312.3</t>
         </is>
       </c>
-      <c r="N55" s="15" t="inlineStr">
-        <is>
-          <t>365625</t>
-        </is>
-      </c>
+      <c r="N55" s="15" t="n"/>
       <c r="O55" s="15" t="inlineStr">
         <is>
           <t>CÁMARA FIJA IP</t>
@@ -8777,11 +8565,7 @@
           <t>ATI 321.5</t>
         </is>
       </c>
-      <c r="N56" s="15" t="inlineStr">
-        <is>
-          <t>460006</t>
-        </is>
-      </c>
+      <c r="N56" s="15" t="n"/>
       <c r="O56" s="15" t="inlineStr">
         <is>
           <t>CÁMARA FIJA IP</t>
@@ -8924,11 +8708,7 @@
           <t>PICV 343 - DCC-3a</t>
         </is>
       </c>
-      <c r="N57" s="15" t="inlineStr">
-        <is>
-          <t>343856</t>
-        </is>
-      </c>
+      <c r="N57" s="15" t="n"/>
       <c r="O57" s="15" t="inlineStr">
         <is>
           <t>CÁMARA FIJA IP</t>
@@ -9071,11 +8851,7 @@
           <t>SE 321 - SUBESTACIÓN ELÉCTRICA SAX</t>
         </is>
       </c>
-      <c r="N58" s="15" t="inlineStr">
-        <is>
-          <t>438478</t>
-        </is>
-      </c>
+      <c r="N58" s="15" t="n"/>
       <c r="O58" s="15" t="inlineStr">
         <is>
           <t>CÁMARA FIJA IP</t>
@@ -9307,11 +9083,7 @@
           <t>Bifurcación Vinalopo</t>
         </is>
       </c>
-      <c r="N60" s="15" t="inlineStr">
-        <is>
-          <t>464480</t>
-        </is>
-      </c>
+      <c r="N60" s="15" t="n"/>
       <c r="O60" s="15" t="inlineStr">
         <is>
           <t>CÁMARA FIJA IP</t>
@@ -9454,11 +9226,7 @@
           <t>PS 468,4 a</t>
         </is>
       </c>
-      <c r="N61" s="15" t="inlineStr">
-        <is>
-          <t>468417</t>
-        </is>
-      </c>
+      <c r="N61" s="15" t="n"/>
       <c r="O61" s="15" t="inlineStr">
         <is>
           <t>CÁMARA FIJA IP</t>
@@ -9779,11 +9547,7 @@
           <t>PS 390,7 a</t>
         </is>
       </c>
-      <c r="N64" s="15" t="inlineStr">
-        <is>
-          <t>390743</t>
-        </is>
-      </c>
+      <c r="N64" s="15" t="n"/>
       <c r="O64" s="15" t="inlineStr">
         <is>
           <t>CÁMARA FIJA IP</t>
@@ -9926,11 +9690,7 @@
           <t>ATI 312.2</t>
         </is>
       </c>
-      <c r="N65" s="15" t="inlineStr">
-        <is>
-          <t>355696</t>
-        </is>
-      </c>
+      <c r="N65" s="15" t="n"/>
       <c r="O65" s="15" t="inlineStr">
         <is>
           <t>CÁMARA FIJA IP</t>
@@ -10073,11 +9833,7 @@
           <t>ET Bifurcación La Oliva (Nudo I)</t>
         </is>
       </c>
-      <c r="N66" s="15" t="inlineStr">
-        <is>
-          <t>410500</t>
-        </is>
-      </c>
+      <c r="N66" s="15" t="n"/>
       <c r="O66" s="15" t="inlineStr">
         <is>
           <t>CÁMARA FIJA IP</t>
@@ -10220,11 +9976,7 @@
           <t>PS 390,7 a</t>
         </is>
       </c>
-      <c r="N67" s="15" t="inlineStr">
-        <is>
-          <t>390743</t>
-        </is>
-      </c>
+      <c r="N67" s="15" t="n"/>
       <c r="O67" s="15" t="inlineStr">
         <is>
           <t>CÁMARA FIJA IP</t>
@@ -10367,11 +10119,7 @@
           <t>SE 321 - SUBESTACIÓN ELÉCTRICA SAX</t>
         </is>
       </c>
-      <c r="N68" s="15" t="inlineStr">
-        <is>
-          <t>438478</t>
-        </is>
-      </c>
+      <c r="N68" s="15" t="n"/>
       <c r="O68" s="15" t="inlineStr">
         <is>
           <t>CÁMARA FIJA IP</t>
@@ -10514,11 +10262,7 @@
           <t>Estación Villena</t>
         </is>
       </c>
-      <c r="N69" s="15" t="inlineStr">
-        <is>
-          <t>435487</t>
-        </is>
-      </c>
+      <c r="N69" s="15" t="n"/>
       <c r="O69" s="15" t="inlineStr">
         <is>
           <t>CÁMARA FIJA IP</t>
@@ -10661,11 +10405,7 @@
           <t>PS 331,2 a</t>
         </is>
       </c>
-      <c r="N70" s="15" t="inlineStr">
-        <is>
-          <t>331283</t>
-        </is>
-      </c>
+      <c r="N70" s="15" t="n"/>
       <c r="O70" s="15" t="inlineStr">
         <is>
           <t>CÁMARA FIJA IP</t>
@@ -10808,11 +10548,7 @@
           <t>PCA Alcoraya</t>
         </is>
       </c>
-      <c r="N71" s="15" t="inlineStr">
-        <is>
-          <t>476931</t>
-        </is>
-      </c>
+      <c r="N71" s="15" t="n"/>
       <c r="O71" s="15" t="inlineStr">
         <is>
           <t>CÁMARA FIJA IP</t>
@@ -10955,11 +10691,7 @@
           <t>PB Caudete AV</t>
         </is>
       </c>
-      <c r="N72" s="15" t="inlineStr">
-        <is>
-          <t>425227</t>
-        </is>
-      </c>
+      <c r="N72" s="15" t="n"/>
       <c r="O72" s="15" t="inlineStr">
         <is>
           <t>CÁMARA FIJA IP</t>
@@ -11102,11 +10834,7 @@
           <t>SE 312 - SUBESTACIÓN ELÉCTRICA CAMPANARIO</t>
         </is>
       </c>
-      <c r="N73" s="15" t="inlineStr">
-        <is>
-          <t>378076</t>
-        </is>
-      </c>
+      <c r="N73" s="15" t="n"/>
       <c r="O73" s="15" t="inlineStr">
         <is>
           <t>CÁMARA FIJA IP</t>
@@ -11249,11 +10977,7 @@
           <t>ET Bifurcación La Oliva (Nudo I)</t>
         </is>
       </c>
-      <c r="N74" s="15" t="inlineStr">
-        <is>
-          <t>410500</t>
-        </is>
-      </c>
+      <c r="N74" s="15" t="n"/>
       <c r="O74" s="15" t="inlineStr">
         <is>
           <t>CÁMARA FIJA IP</t>
@@ -11396,11 +11120,7 @@
           <t>ATI 321.6</t>
         </is>
       </c>
-      <c r="N75" s="15" t="inlineStr">
-        <is>
-          <t>474060</t>
-        </is>
-      </c>
+      <c r="N75" s="15" t="n"/>
       <c r="O75" s="15" t="inlineStr">
         <is>
           <t>CÁMARA FIJA IP</t>
@@ -11543,11 +11263,7 @@
           <t>SE 321 - SUBESTACIÓN ELÉCTRICA SAX</t>
         </is>
       </c>
-      <c r="N76" s="15" t="inlineStr">
-        <is>
-          <t>438478</t>
-        </is>
-      </c>
+      <c r="N76" s="15" t="n"/>
       <c r="O76" s="15" t="inlineStr">
         <is>
           <t>CÁMARA FIJA IP</t>
@@ -11690,11 +11406,7 @@
           <t>VIADUCTO SOBRE A-31</t>
         </is>
       </c>
-      <c r="N77" s="15" t="inlineStr">
-        <is>
-          <t>388771</t>
-        </is>
-      </c>
+      <c r="N77" s="15" t="n"/>
       <c r="O77" s="15" t="inlineStr">
         <is>
           <t>CÁMARA FIJA IP</t>
@@ -11837,11 +11549,7 @@
           <t>PICV 329</t>
         </is>
       </c>
-      <c r="N78" s="15" t="inlineStr">
-        <is>
-          <t>329138</t>
-        </is>
-      </c>
+      <c r="N78" s="15" t="n"/>
       <c r="O78" s="15" t="inlineStr">
         <is>
           <t>CÁMARA FIJA IP</t>
@@ -11984,11 +11692,7 @@
           <t>PS 426,2 a</t>
         </is>
       </c>
-      <c r="N79" s="15" t="inlineStr">
-        <is>
-          <t>426243</t>
-        </is>
-      </c>
+      <c r="N79" s="15" t="n"/>
       <c r="O79" s="15" t="inlineStr">
         <is>
           <t>CÁMARA FIJA IP</t>
@@ -12131,11 +11835,7 @@
           <t>VIADUCTO SOBRE ACEQUIA DEL REY</t>
         </is>
       </c>
-      <c r="N80" s="15" t="inlineStr">
-        <is>
-          <t>431647</t>
-        </is>
-      </c>
+      <c r="N80" s="15" t="n"/>
       <c r="O80" s="15" t="inlineStr">
         <is>
           <t>CÁMARA FIJA IP</t>
@@ -12278,11 +11978,7 @@
           <t>TÚNEL DE LA SIERRA DE LAS ÁGUILAS (1.227m) (boca Alicante)</t>
         </is>
       </c>
-      <c r="N81" s="15" t="inlineStr">
-        <is>
-          <t>470962</t>
-        </is>
-      </c>
+      <c r="N81" s="15" t="n"/>
       <c r="O81" s="15" t="inlineStr">
         <is>
           <t>CÁMARA FIJA IP</t>
@@ -12425,11 +12121,7 @@
           <t>ET PAET Chinchilla AV</t>
         </is>
       </c>
-      <c r="N82" s="15" t="inlineStr">
-        <is>
-          <t>336566</t>
-        </is>
-      </c>
+      <c r="N82" s="15" t="n"/>
       <c r="O82" s="15" t="inlineStr">
         <is>
           <t>CÁMARA FIJA IP</t>
@@ -12572,11 +12264,7 @@
           <t>ATI 312.3</t>
         </is>
       </c>
-      <c r="N83" s="15" t="inlineStr">
-        <is>
-          <t>365625</t>
-        </is>
-      </c>
+      <c r="N83" s="15" t="n"/>
       <c r="O83" s="15" t="inlineStr">
         <is>
           <t>CÁMARA FIJA IP</t>
@@ -12719,11 +12407,7 @@
           <t>BASE DE MANTENIMIENTO MONFORTE DEL CID (NODO-7 NAV</t>
         </is>
       </c>
-      <c r="N84" s="15" t="inlineStr">
-        <is>
-          <t>465134</t>
-        </is>
-      </c>
+      <c r="N84" s="15" t="n"/>
       <c r="O84" s="15" t="inlineStr">
         <is>
           <t>CÁMARA FIJA IP</t>
@@ -12866,11 +12550,7 @@
           <t>ATI 321.7</t>
         </is>
       </c>
-      <c r="N85" s="15" t="inlineStr">
-        <is>
-          <t>481640</t>
-        </is>
-      </c>
+      <c r="N85" s="15" t="n"/>
       <c r="O85" s="15" t="inlineStr">
         <is>
           <t>CÁMARA FIJA IP</t>
@@ -13013,11 +12693,7 @@
           <t>PS 361,6 a</t>
         </is>
       </c>
-      <c r="N86" s="15" t="inlineStr">
-        <is>
-          <t>361619</t>
-        </is>
-      </c>
+      <c r="N86" s="15" t="n"/>
       <c r="O86" s="15" t="inlineStr">
         <is>
           <t>CÁMARA FIJA IP</t>
@@ -13160,11 +12836,7 @@
           <t>PS 322,3a (PS 322,6a)</t>
         </is>
       </c>
-      <c r="N87" s="15" t="inlineStr">
-        <is>
-          <t>322398</t>
-        </is>
-      </c>
+      <c r="N87" s="15" t="n"/>
       <c r="O87" s="15" t="inlineStr">
         <is>
           <t>CÁMARA FIJA IP</t>
@@ -13307,11 +12979,7 @@
           <t>PS 431,1 a</t>
         </is>
       </c>
-      <c r="N88" s="15" t="inlineStr">
-        <is>
-          <t>431159</t>
-        </is>
-      </c>
+      <c r="N88" s="15" t="n"/>
       <c r="O88" s="15" t="inlineStr">
         <is>
           <t>CÁMARA FIJA IP</t>
@@ -13454,11 +13122,7 @@
           <t>VIADUCTO 2 EL HONDO - SCVL-16A (BTS09B)</t>
         </is>
       </c>
-      <c r="N89" s="15" t="inlineStr">
-        <is>
-          <t>393795</t>
-        </is>
-      </c>
+      <c r="N89" s="15" t="n"/>
       <c r="O89" s="15" t="inlineStr">
         <is>
           <t>CÁMARA FIJA IP</t>
@@ -13601,11 +13265,7 @@
           <t>PS 376,9 a</t>
         </is>
       </c>
-      <c r="N90" s="15" t="inlineStr">
-        <is>
-          <t>376992</t>
-        </is>
-      </c>
+      <c r="N90" s="15" t="n"/>
       <c r="O90" s="15" t="inlineStr">
         <is>
           <t>CÁMARA FIJA IP</t>
@@ -13748,11 +13408,7 @@
           <t>PCA Elda</t>
         </is>
       </c>
-      <c r="N91" s="15" t="inlineStr">
-        <is>
-          <t>449554</t>
-        </is>
-      </c>
+      <c r="N91" s="15" t="n"/>
       <c r="O91" s="15" t="inlineStr">
         <is>
           <t>CÁMARA FIJA IP</t>
@@ -13895,11 +13551,7 @@
           <t>TÚNEL DE ACCESO ALICANTE (1.067m) (boca Alicante)</t>
         </is>
       </c>
-      <c r="N92" s="15" t="inlineStr">
-        <is>
-          <t>483956</t>
-        </is>
-      </c>
+      <c r="N92" s="15" t="n"/>
       <c r="O92" s="15" t="inlineStr">
         <is>
           <t>CÁMARA FIJA IP</t>
@@ -14042,11 +13694,7 @@
           <t>PICV 329</t>
         </is>
       </c>
-      <c r="N93" s="15" t="inlineStr">
-        <is>
-          <t>329138</t>
-        </is>
-      </c>
+      <c r="N93" s="15" t="n"/>
       <c r="O93" s="15" t="inlineStr">
         <is>
           <t>CÁMARA FIJA IP</t>
@@ -14189,11 +13837,7 @@
           <t>ATF 312.1</t>
         </is>
       </c>
-      <c r="N94" s="15" t="inlineStr">
-        <is>
-          <t>342890</t>
-        </is>
-      </c>
+      <c r="N94" s="15" t="n"/>
       <c r="O94" s="15" t="inlineStr">
         <is>
           <t>CÁMARA FIJA IP</t>
@@ -14336,11 +13980,7 @@
           <t>ATI 321.6</t>
         </is>
       </c>
-      <c r="N95" s="15" t="inlineStr">
-        <is>
-          <t>474060</t>
-        </is>
-      </c>
+      <c r="N95" s="15" t="n"/>
       <c r="O95" s="15" t="inlineStr">
         <is>
           <t>CÁMARA FIJA IP</t>
@@ -14483,11 +14123,7 @@
           <t>ATI 312.5</t>
         </is>
       </c>
-      <c r="N96" s="15" t="inlineStr">
-        <is>
-          <t>398537</t>
-        </is>
-      </c>
+      <c r="N96" s="15" t="n"/>
       <c r="O96" s="15" t="inlineStr">
         <is>
           <t>CÁMARA FIJA IP</t>
@@ -14630,11 +14266,7 @@
           <t>PS 410,0 a</t>
         </is>
       </c>
-      <c r="N97" s="15" t="inlineStr">
-        <is>
-          <t>410086</t>
-        </is>
-      </c>
+      <c r="N97" s="15" t="n"/>
       <c r="O97" s="15" t="inlineStr">
         <is>
           <t>CÁMARA FIJA IP</t>
@@ -14777,11 +14409,7 @@
           <t>PCA Hoya Gonzalo</t>
         </is>
       </c>
-      <c r="N98" s="15" t="inlineStr">
-        <is>
-          <t>348862</t>
-        </is>
-      </c>
+      <c r="N98" s="15" t="n"/>
       <c r="O98" s="15" t="inlineStr">
         <is>
           <t>CÁMARA FIJA IP</t>
@@ -14924,11 +14552,7 @@
           <t>TÚNEL DE LA SERRETA (301m) (boca Alicante)</t>
         </is>
       </c>
-      <c r="N99" s="15" t="inlineStr">
-        <is>
-          <t>480174</t>
-        </is>
-      </c>
+      <c r="N99" s="15" t="n"/>
       <c r="O99" s="15" t="inlineStr">
         <is>
           <t>CÁMARA FIJA IP</t>
@@ -15071,11 +14695,7 @@
           <t>Bifurcación Murcia</t>
         </is>
       </c>
-      <c r="N100" s="15" t="inlineStr">
-        <is>
-          <t>461719</t>
-        </is>
-      </c>
+      <c r="N100" s="15" t="n"/>
       <c r="O100" s="15" t="inlineStr">
         <is>
           <t>CÁMARA FIJA IP</t>
@@ -15218,11 +14838,7 @@
           <t>PS 442,1 a</t>
         </is>
       </c>
-      <c r="N101" s="15" t="inlineStr">
-        <is>
-          <t>442153</t>
-        </is>
-      </c>
+      <c r="N101" s="15" t="n"/>
       <c r="O101" s="15" t="inlineStr">
         <is>
           <t>CÁMARA FIJA IP</t>
@@ -15365,11 +14981,7 @@
           <t>ATF 312.1</t>
         </is>
       </c>
-      <c r="N102" s="15" t="inlineStr">
-        <is>
-          <t>342890</t>
-        </is>
-      </c>
+      <c r="N102" s="15" t="n"/>
       <c r="O102" s="15" t="inlineStr">
         <is>
           <t>CÁMARA FIJA IP</t>
@@ -15512,11 +15124,7 @@
           <t>PCA Atalaya</t>
         </is>
       </c>
-      <c r="N103" s="15" t="inlineStr">
-        <is>
-          <t>395700</t>
-        </is>
-      </c>
+      <c r="N103" s="15" t="n"/>
       <c r="O103" s="15" t="inlineStr">
         <is>
           <t>CÁMARA FIJA IP</t>
@@ -15659,11 +15267,7 @@
           <t>PS PÉRGOLA Cajón A-31 - TM344,3 a - TL344,5 a</t>
         </is>
       </c>
-      <c r="N104" s="15" t="inlineStr">
-        <is>
-          <t>344398</t>
-        </is>
-      </c>
+      <c r="N104" s="15" t="n"/>
       <c r="O104" s="15" t="inlineStr">
         <is>
           <t>CÁMARA FIJA IP</t>
@@ -15806,11 +15410,7 @@
           <t>PS 331,2 a</t>
         </is>
       </c>
-      <c r="N105" s="15" t="inlineStr">
-        <is>
-          <t>331283</t>
-        </is>
-      </c>
+      <c r="N105" s="15" t="n"/>
       <c r="O105" s="15" t="inlineStr">
         <is>
           <t>CÁMARA FIJA IP</t>
@@ -15953,11 +15553,7 @@
           <t>SE 312 - SUBESTACIÓN ELÉCTRICA CAMPANARIO</t>
         </is>
       </c>
-      <c r="N106" s="15" t="inlineStr">
-        <is>
-          <t>378076</t>
-        </is>
-      </c>
+      <c r="N106" s="15" t="n"/>
       <c r="O106" s="15" t="inlineStr">
         <is>
           <t>CÁMARA FIJA IP</t>
@@ -16100,11 +15696,7 @@
           <t>ATI 321.3</t>
         </is>
       </c>
-      <c r="N107" s="15" t="inlineStr">
-        <is>
-          <t>429607</t>
-        </is>
-      </c>
+      <c r="N107" s="15" t="n"/>
       <c r="O107" s="15" t="inlineStr">
         <is>
           <t>CÁMARA FIJA IP</t>
@@ -16247,11 +15839,7 @@
           <t>ATI 311.5</t>
         </is>
       </c>
-      <c r="N108" s="15" t="inlineStr">
-        <is>
-          <t>330036</t>
-        </is>
-      </c>
+      <c r="N108" s="15" t="n"/>
       <c r="O108" s="15" t="inlineStr">
         <is>
           <t>CÁMARA FIJA IP</t>
@@ -16394,11 +15982,7 @@
           <t>PS 390,2 a</t>
         </is>
       </c>
-      <c r="N109" s="15" t="inlineStr">
-        <is>
-          <t>390204</t>
-        </is>
-      </c>
+      <c r="N109" s="15" t="n"/>
       <c r="O109" s="15" t="inlineStr">
         <is>
           <t>CÁMARA FIJA IP</t>
@@ -16541,11 +16125,7 @@
           <t>Estación Villena</t>
         </is>
       </c>
-      <c r="N110" s="15" t="inlineStr">
-        <is>
-          <t>435487</t>
-        </is>
-      </c>
+      <c r="N110" s="15" t="n"/>
       <c r="O110" s="15" t="inlineStr">
         <is>
           <t>CÁMARA FIJA IP</t>
@@ -16688,11 +16268,7 @@
           <t>PS 477,9 a</t>
         </is>
       </c>
-      <c r="N111" s="15" t="inlineStr">
-        <is>
-          <t>477981</t>
-        </is>
-      </c>
+      <c r="N111" s="15" t="n"/>
       <c r="O111" s="15" t="inlineStr">
         <is>
           <t>CÁMARA FIJA IP</t>
@@ -16835,11 +16411,7 @@
           <t>ATI 312.5</t>
         </is>
       </c>
-      <c r="N112" s="15" t="inlineStr">
-        <is>
-          <t>398537</t>
-        </is>
-      </c>
+      <c r="N112" s="15" t="n"/>
       <c r="O112" s="15" t="inlineStr">
         <is>
           <t>CÁMARA FIJA IP</t>
@@ -16982,11 +16554,7 @@
           <t>Viaducto 2 sobre FC La Encina-Caudete (INI). Nudo La Encina Eje5</t>
         </is>
       </c>
-      <c r="N113" s="15" t="inlineStr">
-        <is>
-          <t>416807</t>
-        </is>
-      </c>
+      <c r="N113" s="15" t="n"/>
       <c r="O113" s="15" t="inlineStr">
         <is>
           <t>CÁMARA FIJA IP</t>
@@ -17129,11 +16697,7 @@
           <t>ET Alacant-Terminal</t>
         </is>
       </c>
-      <c r="N114" s="15" t="inlineStr">
-        <is>
-          <t>483925</t>
-        </is>
-      </c>
+      <c r="N114" s="15" t="n"/>
       <c r="O114" s="15" t="inlineStr">
         <is>
           <t>CÁMARA FIJA IP</t>
@@ -17276,11 +16840,7 @@
           <t>PICV 442 - DCC-5a</t>
         </is>
       </c>
-      <c r="N115" s="15" t="inlineStr">
-        <is>
-          <t>442266</t>
-        </is>
-      </c>
+      <c r="N115" s="15" t="n"/>
       <c r="O115" s="15" t="inlineStr">
         <is>
           <t>CÁMARA FIJA IP</t>
@@ -17423,11 +16983,7 @@
           <t>PS 417,9 a - Eje-4</t>
         </is>
       </c>
-      <c r="N116" s="15" t="inlineStr">
-        <is>
-          <t>417934</t>
-        </is>
-      </c>
+      <c r="N116" s="15" t="n"/>
       <c r="O116" s="15" t="inlineStr">
         <is>
           <t>CÁMARA FIJA IP</t>
@@ -17570,11 +17126,7 @@
           <t>PCA El Salobrejo</t>
         </is>
       </c>
-      <c r="N117" s="15" t="inlineStr">
-        <is>
-          <t>361500</t>
-        </is>
-      </c>
+      <c r="N117" s="15" t="n"/>
       <c r="O117" s="15" t="inlineStr">
         <is>
           <t>CÁMARA FIJA IP</t>
@@ -17806,11 +17358,7 @@
           <t>SE 321 - SUBESTACIÓN ELÉCTRICA SAX</t>
         </is>
       </c>
-      <c r="N119" s="15" t="inlineStr">
-        <is>
-          <t>438478</t>
-        </is>
-      </c>
+      <c r="N119" s="15" t="n"/>
       <c r="O119" s="15" t="inlineStr">
         <is>
           <t>CÁMARA FIJA IP</t>
@@ -17953,11 +17501,7 @@
           <t>ATI 311.5</t>
         </is>
       </c>
-      <c r="N120" s="15" t="inlineStr">
-        <is>
-          <t>330036</t>
-        </is>
-      </c>
+      <c r="N120" s="15" t="n"/>
       <c r="O120" s="15" t="inlineStr">
         <is>
           <t>CÁMARA FIJA IP</t>
@@ -18100,11 +17644,7 @@
           <t>PS 332,8 a</t>
         </is>
       </c>
-      <c r="N121" s="15" t="inlineStr">
-        <is>
-          <t>332851</t>
-        </is>
-      </c>
+      <c r="N121" s="15" t="n"/>
       <c r="O121" s="15" t="inlineStr">
         <is>
           <t>CÁMARA FIJA IP</t>
@@ -18247,11 +17787,7 @@
           <t>PS 325,1 a</t>
         </is>
       </c>
-      <c r="N122" s="15" t="inlineStr">
-        <is>
-          <t>325113</t>
-        </is>
-      </c>
+      <c r="N122" s="15" t="n"/>
       <c r="O122" s="15" t="inlineStr">
         <is>
           <t>CÁMARA FIJA IP</t>
@@ -18394,11 +17930,7 @@
           <t>TÚNEL DE LAS BARRANCADAS (2.856m) (boca Albacete)</t>
         </is>
       </c>
-      <c r="N123" s="15" t="inlineStr">
-        <is>
-          <t>444814</t>
-        </is>
-      </c>
+      <c r="N123" s="15" t="n"/>
       <c r="O123" s="15" t="inlineStr">
         <is>
           <t>CÁMARA FIJA IP</t>
@@ -18541,11 +18073,7 @@
           <t>ATI 311.5</t>
         </is>
       </c>
-      <c r="N124" s="15" t="inlineStr">
-        <is>
-          <t>330036</t>
-        </is>
-      </c>
+      <c r="N124" s="15" t="n"/>
       <c r="O124" s="15" t="inlineStr">
         <is>
           <t>CÁMARA FIJA IP</t>
@@ -18688,11 +18216,7 @@
           <t>ATI 312.3</t>
         </is>
       </c>
-      <c r="N125" s="15" t="inlineStr">
-        <is>
-          <t>365625</t>
-        </is>
-      </c>
+      <c r="N125" s="15" t="n"/>
       <c r="O125" s="15" t="inlineStr">
         <is>
           <t>CÁMARA FIJA IP</t>
@@ -18835,11 +18359,7 @@
           <t>SE 312 - SUBESTACIÓN ELÉCTRICA CAMPANARIO</t>
         </is>
       </c>
-      <c r="N126" s="15" t="inlineStr">
-        <is>
-          <t>378076</t>
-        </is>
-      </c>
+      <c r="N126" s="15" t="n"/>
       <c r="O126" s="15" t="inlineStr">
         <is>
           <t>CÁMARA FIJA IP</t>
@@ -18982,11 +18502,7 @@
           <t>PCA Elda</t>
         </is>
       </c>
-      <c r="N127" s="15" t="inlineStr">
-        <is>
-          <t>449554</t>
-        </is>
-      </c>
+      <c r="N127" s="15" t="n"/>
       <c r="O127" s="15" t="inlineStr">
         <is>
           <t>CÁMARA FIJA IP</t>
@@ -19129,11 +18645,7 @@
           <t>PS 483,5 a</t>
         </is>
       </c>
-      <c r="N128" s="15" t="inlineStr">
-        <is>
-          <t>483564</t>
-        </is>
-      </c>
+      <c r="N128" s="15" t="n"/>
       <c r="O128" s="15" t="inlineStr">
         <is>
           <t>CÁMARA FIJA IP</t>
@@ -19276,11 +18788,7 @@
           <t>PS 347,5 a</t>
         </is>
       </c>
-      <c r="N129" s="15" t="inlineStr">
-        <is>
-          <t>347517</t>
-        </is>
-      </c>
+      <c r="N129" s="15" t="n"/>
       <c r="O129" s="15" t="inlineStr">
         <is>
           <t>CÁMARA FIJA IP</t>
@@ -19423,11 +18931,7 @@
           <t>PS 480,1 a</t>
         </is>
       </c>
-      <c r="N130" s="15" t="inlineStr">
-        <is>
-          <t>480102</t>
-        </is>
-      </c>
+      <c r="N130" s="15" t="n"/>
       <c r="O130" s="15" t="inlineStr">
         <is>
           <t>CÁMARA FIJA IP</t>
@@ -19570,11 +19074,7 @@
           <t>PS 372,2 a</t>
         </is>
       </c>
-      <c r="N131" s="15" t="inlineStr">
-        <is>
-          <t>372221</t>
-        </is>
-      </c>
+      <c r="N131" s="15" t="n"/>
       <c r="O131" s="15" t="inlineStr">
         <is>
           <t>CÁMARA FIJA IP</t>
@@ -19717,11 +19217,7 @@
           <t>ATI 312.2</t>
         </is>
       </c>
-      <c r="N132" s="15" t="inlineStr">
-        <is>
-          <t>355696</t>
-        </is>
-      </c>
+      <c r="N132" s="15" t="n"/>
       <c r="O132" s="15" t="inlineStr">
         <is>
           <t>CÁMARA FIJA IP</t>
@@ -19864,11 +19360,7 @@
           <t>PS 359,2 a</t>
         </is>
       </c>
-      <c r="N133" s="15" t="inlineStr">
-        <is>
-          <t>359260</t>
-        </is>
-      </c>
+      <c r="N133" s="15" t="n"/>
       <c r="O133" s="15" t="inlineStr">
         <is>
           <t>CÁMARA FIJA IP</t>
@@ -20011,11 +19503,7 @@
           <t>PS 433,7 a</t>
         </is>
       </c>
-      <c r="N134" s="15" t="inlineStr">
-        <is>
-          <t>433784</t>
-        </is>
-      </c>
+      <c r="N134" s="15" t="n"/>
       <c r="O134" s="15" t="inlineStr">
         <is>
           <t>CÁMARA FIJA IP</t>
@@ -20158,11 +19646,7 @@
           <t>Estación Villena</t>
         </is>
       </c>
-      <c r="N135" s="15" t="inlineStr">
-        <is>
-          <t>435487</t>
-        </is>
-      </c>
+      <c r="N135" s="15" t="n"/>
       <c r="O135" s="15" t="inlineStr">
         <is>
           <t>CÁMARA FIJA IP</t>
@@ -20305,11 +19789,7 @@
           <t>ATI 312.5</t>
         </is>
       </c>
-      <c r="N136" s="15" t="inlineStr">
-        <is>
-          <t>398537</t>
-        </is>
-      </c>
+      <c r="N136" s="15" t="n"/>
       <c r="O136" s="15" t="inlineStr">
         <is>
           <t>CÁMARA FIJA IP</t>
@@ -20452,11 +19932,7 @@
           <t>ET Alacant-Terminal</t>
         </is>
       </c>
-      <c r="N137" s="15" t="inlineStr">
-        <is>
-          <t>483925</t>
-        </is>
-      </c>
+      <c r="N137" s="15" t="n"/>
       <c r="O137" s="15" t="inlineStr">
         <is>
           <t>CÁMARA FIJA IP</t>
@@ -20599,11 +20075,7 @@
           <t>Estación Villena</t>
         </is>
       </c>
-      <c r="N138" s="15" t="inlineStr">
-        <is>
-          <t>435487</t>
-        </is>
-      </c>
+      <c r="N138" s="15" t="n"/>
       <c r="O138" s="15" t="inlineStr">
         <is>
           <t>CÁMARA FIJA IP</t>
@@ -20746,11 +20218,7 @@
           <t>PS 442,1 a</t>
         </is>
       </c>
-      <c r="N139" s="15" t="inlineStr">
-        <is>
-          <t>442153</t>
-        </is>
-      </c>
+      <c r="N139" s="15" t="n"/>
       <c r="O139" s="15" t="inlineStr">
         <is>
           <t>CÁMARA FIJA IP</t>
@@ -20982,11 +20450,7 @@
           <t>PS 324,8a a A-31 (PS 324,9)</t>
         </is>
       </c>
-      <c r="N141" s="15" t="inlineStr">
-        <is>
-          <t>324768</t>
-        </is>
-      </c>
+      <c r="N141" s="15" t="n"/>
       <c r="O141" s="15" t="inlineStr">
         <is>
           <t>CÁMARA FIJA IP</t>
@@ -21129,11 +20593,7 @@
           <t>Estación Villena</t>
         </is>
       </c>
-      <c r="N142" s="15" t="inlineStr">
-        <is>
-          <t>435487</t>
-        </is>
-      </c>
+      <c r="N142" s="15" t="n"/>
       <c r="O142" s="15" t="inlineStr">
         <is>
           <t>CÁMARA FIJA IP</t>
@@ -21276,11 +20736,7 @@
           <t>Estación Villena</t>
         </is>
       </c>
-      <c r="N143" s="15" t="inlineStr">
-        <is>
-          <t>435487</t>
-        </is>
-      </c>
+      <c r="N143" s="15" t="n"/>
       <c r="O143" s="15" t="inlineStr">
         <is>
           <t>CÁMARA FIJA IP</t>
@@ -21423,11 +20879,7 @@
           <t>Estación Villena</t>
         </is>
       </c>
-      <c r="N144" s="15" t="inlineStr">
-        <is>
-          <t>435487</t>
-        </is>
-      </c>
+      <c r="N144" s="15" t="n"/>
       <c r="O144" s="15" t="inlineStr">
         <is>
           <t>CÁMARA FIJA IP</t>
@@ -21570,11 +21022,7 @@
           <t>PS 430,1 a</t>
         </is>
       </c>
-      <c r="N145" s="15" t="inlineStr">
-        <is>
-          <t>430117</t>
-        </is>
-      </c>
+      <c r="N145" s="15" t="n"/>
       <c r="O145" s="15" t="inlineStr">
         <is>
           <t>CÁMARA FIJA IP</t>
@@ -21717,11 +21165,7 @@
           <t>PS 477,0 a</t>
         </is>
       </c>
-      <c r="N146" s="15" t="inlineStr">
-        <is>
-          <t>477024</t>
-        </is>
-      </c>
+      <c r="N146" s="15" t="n"/>
       <c r="O146" s="15" t="inlineStr">
         <is>
           <t>CÁMARA FIJA IP</t>
@@ -21864,11 +21308,7 @@
           <t>PS 328,6 a</t>
         </is>
       </c>
-      <c r="N147" s="15" t="inlineStr">
-        <is>
-          <t>328611</t>
-        </is>
-      </c>
+      <c r="N147" s="15" t="n"/>
       <c r="O147" s="15" t="inlineStr">
         <is>
           <t>CÁMARA FIJA IP</t>
@@ -22011,11 +21451,7 @@
           <t>PCA El Mugrón</t>
         </is>
       </c>
-      <c r="N148" s="15" t="inlineStr">
-        <is>
-          <t>384772</t>
-        </is>
-      </c>
+      <c r="N148" s="15" t="n"/>
       <c r="O148" s="15" t="inlineStr">
         <is>
           <t>CÁMARA FIJA IP</t>
@@ -22158,11 +21594,7 @@
           <t>PS 374,7 a</t>
         </is>
       </c>
-      <c r="N149" s="15" t="inlineStr">
-        <is>
-          <t>374717</t>
-        </is>
-      </c>
+      <c r="N149" s="15" t="n"/>
       <c r="O149" s="15" t="inlineStr">
         <is>
           <t>CÁMARA FIJA IP</t>
@@ -22305,11 +21737,7 @@
           <t>PS 440,2 a</t>
         </is>
       </c>
-      <c r="N150" s="15" t="inlineStr">
-        <is>
-          <t>440258</t>
-        </is>
-      </c>
+      <c r="N150" s="15" t="n"/>
       <c r="O150" s="15" t="inlineStr">
         <is>
           <t>CÁMARA FIJA IP</t>
@@ -22452,11 +21880,7 @@
           <t>PS 417,9 a - Eje-4</t>
         </is>
       </c>
-      <c r="N151" s="15" t="inlineStr">
-        <is>
-          <t>417934</t>
-        </is>
-      </c>
+      <c r="N151" s="15" t="n"/>
       <c r="O151" s="15" t="inlineStr">
         <is>
           <t>CÁMARA FIJA IP</t>
@@ -22599,11 +22023,7 @@
           <t>POZO BOMBAS TÚNEL</t>
         </is>
       </c>
-      <c r="N152" s="15" t="inlineStr">
-        <is>
-          <t>483956</t>
-        </is>
-      </c>
+      <c r="N152" s="15" t="n"/>
       <c r="O152" s="15" t="inlineStr">
         <is>
           <t>CÁMARA FIJA IP</t>
@@ -22746,11 +22166,7 @@
           <t>PB Las Chozas</t>
         </is>
       </c>
-      <c r="N153" s="15" t="inlineStr">
-        <is>
-          <t>407496</t>
-        </is>
-      </c>
+      <c r="N153" s="15" t="n"/>
       <c r="O153" s="15" t="inlineStr">
         <is>
           <t>CÁMARA FIJA IP</t>
@@ -22889,11 +22305,7 @@
           <t>ATI 312.4</t>
         </is>
       </c>
-      <c r="N154" s="15" t="inlineStr">
-        <is>
-          <t>387772</t>
-        </is>
-      </c>
+      <c r="N154" s="15" t="n"/>
       <c r="O154" s="15" t="inlineStr">
         <is>
           <t>CÁMARA FIJA IP</t>
@@ -23036,11 +22448,7 @@
           <t>PS 387,0 a</t>
         </is>
       </c>
-      <c r="N155" s="15" t="inlineStr">
-        <is>
-          <t>387089</t>
-        </is>
-      </c>
+      <c r="N155" s="15" t="n"/>
       <c r="O155" s="15" t="inlineStr">
         <is>
           <t>CÁMARA FIJA IP</t>
@@ -23183,11 +22591,7 @@
           <t>VIADUCTO DE LA RAMBLA DE SUGEL</t>
         </is>
       </c>
-      <c r="N156" s="15" t="inlineStr">
-        <is>
-          <t>395787</t>
-        </is>
-      </c>
+      <c r="N156" s="15" t="n"/>
       <c r="O156" s="15" t="inlineStr">
         <is>
           <t>CÁMARA FIJA IP</t>
@@ -23330,11 +22734,7 @@
           <t>BASE DE MANTENIMIENTO MONFORTE DEL CID (NODO-8)</t>
         </is>
       </c>
-      <c r="N157" s="15" t="inlineStr">
-        <is>
-          <t>465134</t>
-        </is>
-      </c>
+      <c r="N157" s="15" t="n"/>
       <c r="O157" s="15" t="inlineStr">
         <is>
           <t>CÁMARA FIJA IP</t>
@@ -23477,11 +22877,7 @@
           <t>VIADUCTO SOBRE EL CORDEL DEL CAMINO DE SAX - SCVL-21</t>
         </is>
       </c>
-      <c r="N158" s="15" t="inlineStr">
-        <is>
-          <t>436290</t>
-        </is>
-      </c>
+      <c r="N158" s="15" t="n"/>
       <c r="O158" s="15" t="inlineStr">
         <is>
           <t>CÁMARA FIJA IP</t>
@@ -23624,11 +23020,7 @@
           <t>PS 359,2 a</t>
         </is>
       </c>
-      <c r="N159" s="15" t="inlineStr">
-        <is>
-          <t>359260</t>
-        </is>
-      </c>
+      <c r="N159" s="15" t="n"/>
       <c r="O159" s="15" t="inlineStr">
         <is>
           <t>CÁMARA FIJA IP</t>
@@ -23771,11 +23163,7 @@
           <t>Bifurcación Aguaverde (Nudo II)</t>
         </is>
       </c>
-      <c r="N160" s="15" t="inlineStr">
-        <is>
-          <t>418357</t>
-        </is>
-      </c>
+      <c r="N160" s="15" t="n"/>
       <c r="O160" s="15" t="inlineStr">
         <is>
           <t>CÁMARA FIJA IP</t>
@@ -23918,11 +23306,7 @@
           <t>PS 387,0 a</t>
         </is>
       </c>
-      <c r="N161" s="15" t="inlineStr">
-        <is>
-          <t>387089</t>
-        </is>
-      </c>
+      <c r="N161" s="15" t="n"/>
       <c r="O161" s="15" t="inlineStr">
         <is>
           <t>CÁMARA FIJA IP</t>
@@ -24065,11 +23449,7 @@
           <t>PS 385,4a (PS 385,3 a)</t>
         </is>
       </c>
-      <c r="N162" s="15" t="inlineStr">
-        <is>
-          <t>385406</t>
-        </is>
-      </c>
+      <c r="N162" s="15" t="n"/>
       <c r="O162" s="15" t="inlineStr">
         <is>
           <t>CÁMARA FIJA IP</t>
@@ -24212,11 +23592,7 @@
           <t>PS 466,8 a</t>
         </is>
       </c>
-      <c r="N163" s="15" t="inlineStr">
-        <is>
-          <t>466892</t>
-        </is>
-      </c>
+      <c r="N163" s="15" t="n"/>
       <c r="O163" s="15" t="inlineStr">
         <is>
           <t>CÁMARA FIJA IP</t>
@@ -24359,11 +23735,7 @@
           <t>ATI 312.3</t>
         </is>
       </c>
-      <c r="N164" s="15" t="inlineStr">
-        <is>
-          <t>365625</t>
-        </is>
-      </c>
+      <c r="N164" s="15" t="n"/>
       <c r="O164" s="15" t="inlineStr">
         <is>
           <t>CÁMARA FIJA IP</t>
@@ -24506,11 +23878,7 @@
           <t>ET PAET Chinchilla AV</t>
         </is>
       </c>
-      <c r="N165" s="15" t="inlineStr">
-        <is>
-          <t>336566</t>
-        </is>
-      </c>
+      <c r="N165" s="15" t="n"/>
       <c r="O165" s="15" t="inlineStr">
         <is>
           <t>CÁMARA FIJA IP</t>
@@ -24653,11 +24021,7 @@
           <t>TÚNEL DE ACCESO ALICANTE (1.067m) (boca Alicante)</t>
         </is>
       </c>
-      <c r="N166" s="15" t="inlineStr">
-        <is>
-          <t>483956</t>
-        </is>
-      </c>
+      <c r="N166" s="15" t="n"/>
       <c r="O166" s="15" t="inlineStr">
         <is>
           <t>CÁMARA FIJA IP</t>
@@ -24800,11 +24164,7 @@
           <t>ATI 321.7</t>
         </is>
       </c>
-      <c r="N167" s="15" t="inlineStr">
-        <is>
-          <t>481640</t>
-        </is>
-      </c>
+      <c r="N167" s="15" t="n"/>
       <c r="O167" s="15" t="inlineStr">
         <is>
           <t>CÁMARA FIJA IP</t>
@@ -24947,11 +24307,7 @@
           <t>Estación Villena</t>
         </is>
       </c>
-      <c r="N168" s="15" t="inlineStr">
-        <is>
-          <t>435487</t>
-        </is>
-      </c>
+      <c r="N168" s="15" t="n"/>
       <c r="O168" s="15" t="inlineStr">
         <is>
           <t>CÁMARA FIJA IP</t>
@@ -25183,11 +24539,7 @@
           <t>PS 324,7a a A-31 (PS 324,8)</t>
         </is>
       </c>
-      <c r="N170" s="15" t="inlineStr">
-        <is>
-          <t>324735</t>
-        </is>
-      </c>
+      <c r="N170" s="15" t="n"/>
       <c r="O170" s="15" t="inlineStr">
         <is>
           <t>CÁMARA FIJA IP</t>
@@ -25330,11 +24682,7 @@
           <t>ATI 311.5</t>
         </is>
       </c>
-      <c r="N171" s="15" t="inlineStr">
-        <is>
-          <t>330036</t>
-        </is>
-      </c>
+      <c r="N171" s="15" t="n"/>
       <c r="O171" s="15" t="inlineStr">
         <is>
           <t>CÁMARA FIJA IP</t>
@@ -25477,11 +24825,7 @@
           <t>ATF 321.1</t>
         </is>
       </c>
-      <c r="N172" s="15" t="inlineStr">
-        <is>
-          <t>405999</t>
-        </is>
-      </c>
+      <c r="N172" s="15" t="n"/>
       <c r="O172" s="15" t="inlineStr">
         <is>
           <t>CÁMARA FIJA IP</t>
@@ -25624,11 +24968,7 @@
           <t>PS 329,1a (PS 329,2 a)</t>
         </is>
       </c>
-      <c r="N173" s="15" t="inlineStr">
-        <is>
-          <t>329176</t>
-        </is>
-      </c>
+      <c r="N173" s="15" t="n"/>
       <c r="O173" s="15" t="inlineStr">
         <is>
           <t>CÁMARA FIJA IP</t>
@@ -25771,11 +25111,7 @@
           <t>PICV 343 - DCC-3a</t>
         </is>
       </c>
-      <c r="N174" s="15" t="inlineStr">
-        <is>
-          <t>343856</t>
-        </is>
-      </c>
+      <c r="N174" s="15" t="n"/>
       <c r="O174" s="15" t="inlineStr">
         <is>
           <t>CÁMARA FIJA IP</t>
@@ -25918,11 +25254,7 @@
           <t>PS 364,8 a</t>
         </is>
       </c>
-      <c r="N175" s="15" t="inlineStr">
-        <is>
-          <t>364859</t>
-        </is>
-      </c>
+      <c r="N175" s="15" t="n"/>
       <c r="O175" s="15" t="inlineStr">
         <is>
           <t>CÁMARA FIJA IP</t>
@@ -26065,11 +25397,7 @@
           <t>Bifurcación Aguaverde (Nudo II)</t>
         </is>
       </c>
-      <c r="N176" s="15" t="inlineStr">
-        <is>
-          <t>418357</t>
-        </is>
-      </c>
+      <c r="N176" s="15" t="n"/>
       <c r="O176" s="15" t="inlineStr">
         <is>
           <t>CÁMARA FIJA IP</t>
@@ -26212,11 +25540,7 @@
           <t>Estación Villena</t>
         </is>
       </c>
-      <c r="N177" s="15" t="inlineStr">
-        <is>
-          <t>435487</t>
-        </is>
-      </c>
+      <c r="N177" s="15" t="n"/>
       <c r="O177" s="15" t="inlineStr">
         <is>
           <t>CÁMARA FIJA IP</t>
@@ -26359,11 +25683,7 @@
           <t>ET Bifurcación La Oliva (Nudo I)</t>
         </is>
       </c>
-      <c r="N178" s="15" t="inlineStr">
-        <is>
-          <t>410500</t>
-        </is>
-      </c>
+      <c r="N178" s="15" t="n"/>
       <c r="O178" s="15" t="inlineStr">
         <is>
           <t>CÁMARA FIJA IP</t>
@@ -26506,11 +25826,7 @@
           <t>PS 321,7a (PS 321,9a)</t>
         </is>
       </c>
-      <c r="N179" s="15" t="inlineStr">
-        <is>
-          <t>321770</t>
-        </is>
-      </c>
+      <c r="N179" s="15" t="n"/>
       <c r="O179" s="15" t="inlineStr">
         <is>
           <t>CÁMARA FIJA IP</t>
@@ -26653,11 +25969,7 @@
           <t>PCA El Salobrejo</t>
         </is>
       </c>
-      <c r="N180" s="15" t="inlineStr">
-        <is>
-          <t>361500</t>
-        </is>
-      </c>
+      <c r="N180" s="15" t="n"/>
       <c r="O180" s="15" t="inlineStr">
         <is>
           <t>CÁMARA FIJA IP</t>
@@ -26800,11 +26112,7 @@
           <t>ATI 312.2</t>
         </is>
       </c>
-      <c r="N181" s="15" t="inlineStr">
-        <is>
-          <t>355696</t>
-        </is>
-      </c>
+      <c r="N181" s="15" t="n"/>
       <c r="O181" s="15" t="inlineStr">
         <is>
           <t>CÁMARA FIJA IP</t>
@@ -26947,11 +26255,7 @@
           <t>POZO BOMBAS TÚNEL</t>
         </is>
       </c>
-      <c r="N182" s="15" t="inlineStr">
-        <is>
-          <t>483956</t>
-        </is>
-      </c>
+      <c r="N182" s="15" t="n"/>
       <c r="O182" s="15" t="inlineStr">
         <is>
           <t>CÁMARA FIJA IP</t>
@@ -27094,11 +26398,7 @@
           <t>PS 466,8 a</t>
         </is>
       </c>
-      <c r="N183" s="15" t="inlineStr">
-        <is>
-          <t>466892</t>
-        </is>
-      </c>
+      <c r="N183" s="15" t="n"/>
       <c r="O183" s="15" t="inlineStr">
         <is>
           <t>CÁMARA FIJA IP</t>
@@ -27241,11 +26541,7 @@
           <t>BASE DE MANTENIMIENTO MONFORTE DEL CID (NODO-7 NAV</t>
         </is>
       </c>
-      <c r="N184" s="15" t="inlineStr">
-        <is>
-          <t>465134</t>
-        </is>
-      </c>
+      <c r="N184" s="15" t="n"/>
       <c r="O184" s="15" t="inlineStr">
         <is>
           <t>CÁMARA FIJA IP</t>
@@ -27388,11 +26684,7 @@
           <t>ATI 321.4</t>
         </is>
       </c>
-      <c r="N185" s="15" t="inlineStr">
-        <is>
-          <t>450660</t>
-        </is>
-      </c>
+      <c r="N185" s="15" t="n"/>
       <c r="O185" s="15" t="inlineStr">
         <is>
           <t>CÁMARA FIJA IP</t>
@@ -27535,11 +26827,7 @@
           <t>ATI 321.4</t>
         </is>
       </c>
-      <c r="N186" s="15" t="inlineStr">
-        <is>
-          <t>450660</t>
-        </is>
-      </c>
+      <c r="N186" s="15" t="n"/>
       <c r="O186" s="15" t="inlineStr">
         <is>
           <t>CÁMARA FIJA IP</t>
@@ -27682,11 +26970,7 @@
           <t>PS 428,7 a</t>
         </is>
       </c>
-      <c r="N187" s="15" t="inlineStr">
-        <is>
-          <t>428763</t>
-        </is>
-      </c>
+      <c r="N187" s="15" t="n"/>
       <c r="O187" s="15" t="inlineStr">
         <is>
           <t>CÁMARA FIJA IP</t>
@@ -27829,11 +27113,7 @@
           <t>ATI 321.6</t>
         </is>
       </c>
-      <c r="N188" s="15" t="inlineStr">
-        <is>
-          <t>474060</t>
-        </is>
-      </c>
+      <c r="N188" s="15" t="n"/>
       <c r="O188" s="15" t="inlineStr">
         <is>
           <t>CÁMARA FIJA IP</t>
@@ -27976,11 +27256,7 @@
           <t>ET Bifurcación La Oliva (Nudo I)</t>
         </is>
       </c>
-      <c r="N189" s="15" t="inlineStr">
-        <is>
-          <t>410500</t>
-        </is>
-      </c>
+      <c r="N189" s="15" t="n"/>
       <c r="O189" s="15" t="inlineStr">
         <is>
           <t>CÁMARA FIJA IP</t>
@@ -28123,11 +27399,7 @@
           <t>ATF 312.1</t>
         </is>
       </c>
-      <c r="N190" s="15" t="inlineStr">
-        <is>
-          <t>342890</t>
-        </is>
-      </c>
+      <c r="N190" s="15" t="n"/>
       <c r="O190" s="15" t="inlineStr">
         <is>
           <t>CÁMARA FIJA IP</t>
@@ -28270,11 +27542,7 @@
           <t>ATI 321.3</t>
         </is>
       </c>
-      <c r="N191" s="15" t="inlineStr">
-        <is>
-          <t>429607</t>
-        </is>
-      </c>
+      <c r="N191" s="15" t="n"/>
       <c r="O191" s="15" t="inlineStr">
         <is>
           <t>CÁMARA FIJA IP</t>
@@ -28417,11 +27685,7 @@
           <t>VIADUCTO SOBRE FC MADRID-ALICANTE</t>
         </is>
       </c>
-      <c r="N192" s="15" t="inlineStr">
-        <is>
-          <t>420867</t>
-        </is>
-      </c>
+      <c r="N192" s="15" t="n"/>
       <c r="O192" s="15" t="inlineStr">
         <is>
           <t>CÁMARA FIJA IP</t>
@@ -28564,11 +27828,7 @@
           <t>PS 367,2 a</t>
         </is>
       </c>
-      <c r="N193" s="15" t="inlineStr">
-        <is>
-          <t>367224</t>
-        </is>
-      </c>
+      <c r="N193" s="15" t="n"/>
       <c r="O193" s="15" t="inlineStr">
         <is>
           <t>CÁMARA FIJA IP</t>
@@ -28711,11 +27971,7 @@
           <t>ET PAET Villena AV</t>
         </is>
       </c>
-      <c r="N194" s="15" t="inlineStr">
-        <is>
-          <t>435487</t>
-        </is>
-      </c>
+      <c r="N194" s="15" t="n"/>
       <c r="O194" s="15" t="inlineStr">
         <is>
           <t>CÁMARA FIJA IP</t>
@@ -28858,11 +28114,7 @@
           <t>TÚNEL DE LA SERRETA (301m) (boca Alicante)</t>
         </is>
       </c>
-      <c r="N195" s="15" t="inlineStr">
-        <is>
-          <t>480174</t>
-        </is>
-      </c>
+      <c r="N195" s="15" t="n"/>
       <c r="O195" s="15" t="inlineStr">
         <is>
           <t>CÁMARA FIJA IP</t>
@@ -29005,11 +28257,7 @@
           <t>ATI 321.4</t>
         </is>
       </c>
-      <c r="N196" s="15" t="inlineStr">
-        <is>
-          <t>450660</t>
-        </is>
-      </c>
+      <c r="N196" s="15" t="n"/>
       <c r="O196" s="15" t="inlineStr">
         <is>
           <t>CÁMARA FIJA IP</t>
@@ -29152,11 +28400,7 @@
           <t>ATI 321.7</t>
         </is>
       </c>
-      <c r="N197" s="15" t="inlineStr">
-        <is>
-          <t>481640</t>
-        </is>
-      </c>
+      <c r="N197" s="15" t="n"/>
       <c r="O197" s="15" t="inlineStr">
         <is>
           <t>CÁMARA FIJA IP</t>
@@ -29299,11 +28543,7 @@
           <t>ATI 312.5</t>
         </is>
       </c>
-      <c r="N198" s="15" t="inlineStr">
-        <is>
-          <t>398537</t>
-        </is>
-      </c>
+      <c r="N198" s="15" t="n"/>
       <c r="O198" s="15" t="inlineStr">
         <is>
           <t>CÁMARA FIJA IP</t>
@@ -29446,11 +28686,7 @@
           <t>Estación Villena</t>
         </is>
       </c>
-      <c r="N199" s="15" t="inlineStr">
-        <is>
-          <t>435487</t>
-        </is>
-      </c>
+      <c r="N199" s="15" t="n"/>
       <c r="O199" s="15" t="inlineStr">
         <is>
           <t>CÁMARA FIJA IP</t>
@@ -29593,11 +28829,7 @@
           <t>BTS 11A</t>
         </is>
       </c>
-      <c r="N200" s="15" t="inlineStr">
-        <is>
-          <t>405200</t>
-        </is>
-      </c>
+      <c r="N200" s="15" t="n"/>
       <c r="O200" s="15" t="inlineStr">
         <is>
           <t>CÁMARA DOMO IP</t>
@@ -29740,11 +28972,7 @@
           <t>VIADUCTO SOBRE CV-824 - SCVL-25A (BTS20A)</t>
         </is>
       </c>
-      <c r="N201" s="15" t="inlineStr">
-        <is>
-          <t>473530</t>
-        </is>
-      </c>
+      <c r="N201" s="15" t="n"/>
       <c r="O201" s="15" t="inlineStr">
         <is>
           <t>CÁMARA DOMO IP</t>
@@ -29887,11 +29115,7 @@
           <t>BTS 13B - SCVL20A</t>
         </is>
       </c>
-      <c r="N202" s="15" t="inlineStr">
-        <is>
-          <t>426207</t>
-        </is>
-      </c>
+      <c r="N202" s="15" t="n"/>
       <c r="O202" s="15" t="inlineStr">
         <is>
           <t>CÁMARA DOMO IP</t>
@@ -30034,11 +29258,7 @@
           <t>ET PAET Chinchilla AV</t>
         </is>
       </c>
-      <c r="N203" s="15" t="inlineStr">
-        <is>
-          <t>336566</t>
-        </is>
-      </c>
+      <c r="N203" s="15" t="n"/>
       <c r="O203" s="15" t="inlineStr">
         <is>
           <t>CÁMARA DOMO IP</t>
@@ -30181,11 +29401,7 @@
           <t>BTS 18B</t>
         </is>
       </c>
-      <c r="N204" s="15" t="inlineStr">
-        <is>
-          <t>463781</t>
-        </is>
-      </c>
+      <c r="N204" s="15" t="n"/>
       <c r="O204" s="15" t="inlineStr">
         <is>
           <t>CÁMARA DOMO IP</t>
@@ -30328,11 +29544,7 @@
           <t>ATI 321.7</t>
         </is>
       </c>
-      <c r="N205" s="15" t="inlineStr">
-        <is>
-          <t>481640</t>
-        </is>
-      </c>
+      <c r="N205" s="15" t="n"/>
       <c r="O205" s="15" t="inlineStr">
         <is>
           <t>CÁMARA DOMO IP</t>
@@ -30475,11 +29687,7 @@
           <t>VIADUCTO SOBRE LA A-7</t>
         </is>
       </c>
-      <c r="N206" s="15" t="inlineStr">
-        <is>
-          <t>481876</t>
-        </is>
-      </c>
+      <c r="N206" s="15" t="n"/>
       <c r="O206" s="15" t="inlineStr">
         <is>
           <t>CÁMARA DOMO IP</t>
@@ -30622,11 +29830,7 @@
           <t>ET PAET Chinchilla AV</t>
         </is>
       </c>
-      <c r="N207" s="15" t="inlineStr">
-        <is>
-          <t>336566</t>
-        </is>
-      </c>
+      <c r="N207" s="15" t="n"/>
       <c r="O207" s="15" t="inlineStr">
         <is>
           <t>CÁMARA DOMO IP</t>
@@ -30769,11 +29973,7 @@
           <t>TÚNEL V2 Nodo-10</t>
         </is>
       </c>
-      <c r="N208" s="15" t="inlineStr">
-        <is>
-          <t>483956</t>
-        </is>
-      </c>
+      <c r="N208" s="15" t="n"/>
       <c r="O208" s="15" t="inlineStr">
         <is>
           <t>CÁMARA DOMO IP</t>
@@ -30916,11 +30116,7 @@
           <t>VIADUCTO SOBRE ACEQUIA DEL REY</t>
         </is>
       </c>
-      <c r="N209" s="15" t="inlineStr">
-        <is>
-          <t>431647</t>
-        </is>
-      </c>
+      <c r="N209" s="15" t="n"/>
       <c r="O209" s="15" t="inlineStr">
         <is>
           <t>CÁMARA DOMO IP</t>
@@ -31063,11 +30259,7 @@
           <t>BTS 20B</t>
         </is>
       </c>
-      <c r="N210" s="15" t="inlineStr">
-        <is>
-          <t>476032</t>
-        </is>
-      </c>
+      <c r="N210" s="15" t="n"/>
       <c r="O210" s="15" t="inlineStr">
         <is>
           <t>CÁMARA DOMO IP</t>
@@ -31210,11 +30402,7 @@
           <t>BTS 06A</t>
         </is>
       </c>
-      <c r="N211" s="15" t="inlineStr">
-        <is>
-          <t>367700</t>
-        </is>
-      </c>
+      <c r="N211" s="15" t="n"/>
       <c r="O211" s="15" t="inlineStr">
         <is>
           <t>CÁMARA DOMO IP</t>
@@ -31357,11 +30545,7 @@
           <t>TÚNEL DE LA SERRETA (301m) (boca Alicante)</t>
         </is>
       </c>
-      <c r="N212" s="15" t="inlineStr">
-        <is>
-          <t>480174</t>
-        </is>
-      </c>
+      <c r="N212" s="15" t="n"/>
       <c r="O212" s="15" t="inlineStr">
         <is>
           <t>CÁMARA DOMO IP</t>
@@ -31504,11 +30688,7 @@
           <t>TÚNEL DE ACCESO ALICANTE (1.067m) (boca Alicante)</t>
         </is>
       </c>
-      <c r="N213" s="15" t="inlineStr">
-        <is>
-          <t>483956</t>
-        </is>
-      </c>
+      <c r="N213" s="15" t="n"/>
       <c r="O213" s="15" t="inlineStr">
         <is>
           <t>CÁMARA DOMO IP</t>
@@ -31651,11 +30831,7 @@
           <t>TÚNEL V1 Nodo-3</t>
         </is>
       </c>
-      <c r="N214" s="15" t="inlineStr">
-        <is>
-          <t>483956</t>
-        </is>
-      </c>
+      <c r="N214" s="15" t="n"/>
       <c r="O214" s="15" t="inlineStr">
         <is>
           <t>CÁMARA DOMO IP</t>
@@ -31798,11 +30974,7 @@
           <t>SE 321 - SUBESTACIÓN ELÉCTRICA SAX</t>
         </is>
       </c>
-      <c r="N215" s="15" t="inlineStr">
-        <is>
-          <t>438478</t>
-        </is>
-      </c>
+      <c r="N215" s="15" t="n"/>
       <c r="O215" s="15" t="inlineStr">
         <is>
           <t>CÁMARA DOMO IP</t>
@@ -31945,11 +31117,7 @@
           <t>BTS01B - SCVL-9A</t>
         </is>
       </c>
-      <c r="N216" s="15" t="inlineStr">
-        <is>
-          <t>327918</t>
-        </is>
-      </c>
+      <c r="N216" s="15" t="n"/>
       <c r="O216" s="15" t="inlineStr">
         <is>
           <t>CÁMARA DOMO IP</t>
@@ -32092,11 +31260,7 @@
           <t>SE 312 - SUBESTACIÓN ELÉCTRICA CAMPANARIO</t>
         </is>
       </c>
-      <c r="N217" s="15" t="inlineStr">
-        <is>
-          <t>378076</t>
-        </is>
-      </c>
+      <c r="N217" s="15" t="n"/>
       <c r="O217" s="15" t="inlineStr">
         <is>
           <t>CÁMARA DOMO IP</t>
@@ -32239,11 +31403,7 @@
           <t>VIADUCTO SOBRE FFCC LA ENCINA-ALICANTE</t>
         </is>
       </c>
-      <c r="N218" s="15" t="inlineStr">
-        <is>
-          <t>455844</t>
-        </is>
-      </c>
+      <c r="N218" s="15" t="n"/>
       <c r="O218" s="15" t="inlineStr">
         <is>
           <t>CÁMARA DOMO IP</t>
@@ -32475,11 +31635,7 @@
           <t>BTS 10A</t>
         </is>
       </c>
-      <c r="N220" s="15" t="inlineStr">
-        <is>
-          <t>398047</t>
-        </is>
-      </c>
+      <c r="N220" s="15" t="n"/>
       <c r="O220" s="15" t="inlineStr">
         <is>
           <t>CÁMARA DOMO IP</t>
@@ -32622,11 +31778,7 @@
           <t>BTS 15A</t>
         </is>
       </c>
-      <c r="N221" s="15" t="inlineStr">
-        <is>
-          <t>437951</t>
-        </is>
-      </c>
+      <c r="N221" s="15" t="n"/>
       <c r="O221" s="15" t="inlineStr">
         <is>
           <t>CÁMARA DOMO IP</t>
@@ -32769,11 +31921,7 @@
           <t>VIADUCTO - SCVL-14A (BTS08A)</t>
         </is>
       </c>
-      <c r="N222" s="15" t="inlineStr">
-        <is>
-          <t>382592</t>
-        </is>
-      </c>
+      <c r="N222" s="15" t="n"/>
       <c r="O222" s="15" t="inlineStr">
         <is>
           <t>CÁMARA DOMO IP</t>
@@ -32916,11 +32064,7 @@
           <t>Estación Villena</t>
         </is>
       </c>
-      <c r="N223" s="15" t="inlineStr">
-        <is>
-          <t>435487</t>
-        </is>
-      </c>
+      <c r="N223" s="15" t="n"/>
       <c r="O223" s="15" t="inlineStr">
         <is>
           <t>CÁMARA DOMO IP</t>
@@ -33063,11 +32207,7 @@
           <t>TÚNEL DE ACCESO ALICANTE (1.067m) (boca Alicante)</t>
         </is>
       </c>
-      <c r="N224" s="15" t="inlineStr">
-        <is>
-          <t>483956</t>
-        </is>
-      </c>
+      <c r="N224" s="15" t="n"/>
       <c r="O224" s="15" t="inlineStr">
         <is>
           <t>CÁMARA DOMO IP</t>
@@ -33210,11 +32350,7 @@
           <t>VIADUCTO SOBRE BARRANCO DE LOS BALADRES</t>
         </is>
       </c>
-      <c r="N225" s="15" t="inlineStr">
-        <is>
-          <t>457504</t>
-        </is>
-      </c>
+      <c r="N225" s="15" t="n"/>
       <c r="O225" s="15" t="inlineStr">
         <is>
           <t>CÁMARA DOMO IP</t>
@@ -33357,11 +32493,7 @@
           <t>Estación Villena</t>
         </is>
       </c>
-      <c r="N226" s="15" t="inlineStr">
-        <is>
-          <t>435487</t>
-        </is>
-      </c>
+      <c r="N226" s="15" t="n"/>
       <c r="O226" s="15" t="inlineStr">
         <is>
           <t>CÁMARA DOMO IP</t>
@@ -33504,11 +32636,7 @@
           <t>BTS 05A</t>
         </is>
       </c>
-      <c r="N227" s="15" t="inlineStr">
-        <is>
-          <t>358916</t>
-        </is>
-      </c>
+      <c r="N227" s="15" t="n"/>
       <c r="O227" s="15" t="inlineStr">
         <is>
           <t>CÁMARA DOMO IP</t>
@@ -33740,11 +32868,7 @@
           <t>TÚNEL V2 Nodo-11</t>
         </is>
       </c>
-      <c r="N229" s="15" t="inlineStr">
-        <is>
-          <t>483956</t>
-        </is>
-      </c>
+      <c r="N229" s="15" t="n"/>
       <c r="O229" s="15" t="inlineStr">
         <is>
           <t>CÁMARA DOMO IP</t>
@@ -33974,11 +33098,7 @@
           <t>BTS 16B (3 FOR + 4 FOR-OP)</t>
         </is>
       </c>
-      <c r="N231" s="15" t="inlineStr">
-        <is>
-          <t>448927</t>
-        </is>
-      </c>
+      <c r="N231" s="15" t="n"/>
       <c r="O231" s="15" t="inlineStr">
         <is>
           <t>CÁMARA DOMO IP</t>
@@ -34121,11 +33241,7 @@
           <t>VIADUCTO SOBRE EL CORDEL DEL CAMINO DE SAX - SCVL-21</t>
         </is>
       </c>
-      <c r="N232" s="15" t="inlineStr">
-        <is>
-          <t>436290</t>
-        </is>
-      </c>
+      <c r="N232" s="15" t="n"/>
       <c r="O232" s="15" t="inlineStr">
         <is>
           <t>CÁMARA DOMO IP</t>
@@ -34268,11 +33384,7 @@
           <t>Estación Villena</t>
         </is>
       </c>
-      <c r="N233" s="15" t="inlineStr">
-        <is>
-          <t>435487</t>
-        </is>
-      </c>
+      <c r="N233" s="15" t="n"/>
       <c r="O233" s="15" t="inlineStr">
         <is>
           <t>CÁMARA DOMO IP</t>
@@ -34415,11 +33527,7 @@
           <t>BTS 17A - SCVL-22A</t>
         </is>
       </c>
-      <c r="N234" s="15" t="inlineStr">
-        <is>
-          <t>450640</t>
-        </is>
-      </c>
+      <c r="N234" s="15" t="n"/>
       <c r="O234" s="15" t="inlineStr">
         <is>
           <t>CÁMARA DOMO IP</t>
@@ -34562,11 +33670,7 @@
           <t>ATI 321.5</t>
         </is>
       </c>
-      <c r="N235" s="15" t="inlineStr">
-        <is>
-          <t>460006</t>
-        </is>
-      </c>
+      <c r="N235" s="15" t="n"/>
       <c r="O235" s="15" t="inlineStr">
         <is>
           <t>CÁMARA DOMO IP</t>
@@ -34709,11 +33813,7 @@
           <t>Estación Villena</t>
         </is>
       </c>
-      <c r="N236" s="15" t="inlineStr">
-        <is>
-          <t>435487</t>
-        </is>
-      </c>
+      <c r="N236" s="15" t="n"/>
       <c r="O236" s="15" t="inlineStr">
         <is>
           <t>CÁMARA DOMO IP</t>
@@ -34856,11 +33956,7 @@
           <t>TÚNEL DE LA SIERRA DE LAS ÁGUILAS (1.227m) (boca Alicante)</t>
         </is>
       </c>
-      <c r="N237" s="15" t="inlineStr">
-        <is>
-          <t>470962</t>
-        </is>
-      </c>
+      <c r="N237" s="15" t="n"/>
       <c r="O237" s="15" t="inlineStr">
         <is>
           <t>CÁMARA DOMO IP</t>
@@ -35003,11 +34099,7 @@
           <t>BTS 14B</t>
         </is>
       </c>
-      <c r="N238" s="15" t="inlineStr">
-        <is>
-          <t>433760</t>
-        </is>
-      </c>
+      <c r="N238" s="15" t="n"/>
       <c r="O238" s="15" t="inlineStr">
         <is>
           <t>CÁMARA DOMO IP</t>
@@ -35150,11 +34242,7 @@
           <t>TÚNEL V2 Nodo-13</t>
         </is>
       </c>
-      <c r="N239" s="15" t="inlineStr">
-        <is>
-          <t>483956</t>
-        </is>
-      </c>
+      <c r="N239" s="15" t="n"/>
       <c r="O239" s="15" t="inlineStr">
         <is>
           <t>CÁMARA DOMO IP</t>
@@ -35297,11 +34385,7 @@
           <t>BTS 21B (CT 5 Túnel de La Serreta)</t>
         </is>
       </c>
-      <c r="N240" s="15" t="inlineStr">
-        <is>
-          <t>480160</t>
-        </is>
-      </c>
+      <c r="N240" s="15" t="n"/>
       <c r="O240" s="15" t="inlineStr">
         <is>
           <t>CÁMARA DOMO IP</t>
@@ -35444,11 +34528,7 @@
           <t>BTS 05B</t>
         </is>
       </c>
-      <c r="N241" s="15" t="inlineStr">
-        <is>
-          <t>363923</t>
-        </is>
-      </c>
+      <c r="N241" s="15" t="n"/>
       <c r="O241" s="15" t="inlineStr">
         <is>
           <t>CÁMARA DOMO IP</t>
@@ -35591,11 +34671,7 @@
           <t>BTS01A</t>
         </is>
       </c>
-      <c r="N242" s="15" t="inlineStr">
-        <is>
-          <t>323340</t>
-        </is>
-      </c>
+      <c r="N242" s="15" t="n"/>
       <c r="O242" s="15" t="inlineStr">
         <is>
           <t>CÁMARA DOMO IP</t>
@@ -35738,11 +34814,7 @@
           <t>TÚNEL V2 Nodo-9</t>
         </is>
       </c>
-      <c r="N243" s="15" t="inlineStr">
-        <is>
-          <t>483956</t>
-        </is>
-      </c>
+      <c r="N243" s="15" t="n"/>
       <c r="O243" s="15" t="inlineStr">
         <is>
           <t>CÁMARA DOMO IP</t>
@@ -35885,11 +34957,7 @@
           <t>BTS 08A</t>
         </is>
       </c>
-      <c r="N244" s="15" t="inlineStr">
-        <is>
-          <t>383493</t>
-        </is>
-      </c>
+      <c r="N244" s="15" t="n"/>
       <c r="O244" s="15" t="inlineStr">
         <is>
           <t>CÁMARA DOMO IP</t>
@@ -36032,11 +35100,7 @@
           <t>VIADUCTO 2 EL HONDO - SCVL-16A (BTS09B)</t>
         </is>
       </c>
-      <c r="N245" s="15" t="inlineStr">
-        <is>
-          <t>393795</t>
-        </is>
-      </c>
+      <c r="N245" s="15" t="n"/>
       <c r="O245" s="15" t="inlineStr">
         <is>
           <t>CÁMARA DOMO IP</t>
@@ -36179,11 +35243,7 @@
           <t>TÚNEL V1 Nodo-7</t>
         </is>
       </c>
-      <c r="N246" s="15" t="inlineStr">
-        <is>
-          <t>483956</t>
-        </is>
-      </c>
+      <c r="N246" s="15" t="n"/>
       <c r="O246" s="15" t="inlineStr">
         <is>
           <t>CÁMARA DOMO IP</t>
@@ -36326,11 +35386,7 @@
           <t>BTS 04B - SCVL-11A</t>
         </is>
       </c>
-      <c r="N247" s="15" t="inlineStr">
-        <is>
-          <t>355160</t>
-        </is>
-      </c>
+      <c r="N247" s="15" t="n"/>
       <c r="O247" s="15" t="inlineStr">
         <is>
           <t>CÁMARA DOMO IP</t>
@@ -36473,11 +35529,7 @@
           <t>ATI 321.6</t>
         </is>
       </c>
-      <c r="N248" s="15" t="inlineStr">
-        <is>
-          <t>474060</t>
-        </is>
-      </c>
+      <c r="N248" s="15" t="n"/>
       <c r="O248" s="15" t="inlineStr">
         <is>
           <t>CÁMARA DOMO IP</t>
@@ -36620,11 +35672,7 @@
           <t>BTS03A</t>
         </is>
       </c>
-      <c r="N249" s="15" t="inlineStr">
-        <is>
-          <t>342828</t>
-        </is>
-      </c>
+      <c r="N249" s="15" t="n"/>
       <c r="O249" s="15" t="inlineStr">
         <is>
           <t>CÁMARA DOMO IP</t>
@@ -36767,11 +35815,7 @@
           <t>ATI 311.5</t>
         </is>
       </c>
-      <c r="N250" s="15" t="inlineStr">
-        <is>
-          <t>330036</t>
-        </is>
-      </c>
+      <c r="N250" s="15" t="n"/>
       <c r="O250" s="15" t="inlineStr">
         <is>
           <t>CÁMARA DOMO IP</t>
@@ -36914,11 +35958,7 @@
           <t>BTS 03B</t>
         </is>
       </c>
-      <c r="N251" s="15" t="inlineStr">
-        <is>
-          <t>347556</t>
-        </is>
-      </c>
+      <c r="N251" s="15" t="n"/>
       <c r="O251" s="15" t="inlineStr">
         <is>
           <t>CÁMARA DOMO IP</t>
@@ -37061,11 +36101,7 @@
           <t>TÚNEL V1 Nodo-6</t>
         </is>
       </c>
-      <c r="N252" s="15" t="inlineStr">
-        <is>
-          <t>483956</t>
-        </is>
-      </c>
+      <c r="N252" s="15" t="n"/>
       <c r="O252" s="15" t="inlineStr">
         <is>
           <t>CÁMARA DOMO IP</t>
@@ -37208,11 +36244,7 @@
           <t>Estación Villena</t>
         </is>
       </c>
-      <c r="N253" s="15" t="inlineStr">
-        <is>
-          <t>435487</t>
-        </is>
-      </c>
+      <c r="N253" s="15" t="n"/>
       <c r="O253" s="15" t="inlineStr">
         <is>
           <t>CÁMARA DOMO IP</t>
@@ -37355,11 +36387,7 @@
           <t>TÚNEL V1 Nodo-1</t>
         </is>
       </c>
-      <c r="N254" s="15" t="inlineStr">
-        <is>
-          <t>483956</t>
-        </is>
-      </c>
+      <c r="N254" s="15" t="n"/>
       <c r="O254" s="15" t="inlineStr">
         <is>
           <t>CÁMARA DOMO IP</t>
@@ -37502,11 +36530,7 @@
           <t>ATI 321.3</t>
         </is>
       </c>
-      <c r="N255" s="15" t="inlineStr">
-        <is>
-          <t>429607</t>
-        </is>
-      </c>
+      <c r="N255" s="15" t="n"/>
       <c r="O255" s="15" t="inlineStr">
         <is>
           <t>CÁMARA DOMO IP</t>
@@ -37649,11 +36673,7 @@
           <t>VIADUCTO SOBRE FC</t>
         </is>
       </c>
-      <c r="N256" s="15" t="inlineStr">
-        <is>
-          <t>468993</t>
-        </is>
-      </c>
+      <c r="N256" s="15" t="n"/>
       <c r="O256" s="15" t="inlineStr">
         <is>
           <t>CÁMARA DOMO IP</t>
@@ -37885,11 +36905,7 @@
           <t>BTS 22B (3 FOR) (SOLO BTS, SIN BTO)</t>
         </is>
       </c>
-      <c r="N258" s="15" t="inlineStr">
-        <is>
-          <t>482308</t>
-        </is>
-      </c>
+      <c r="N258" s="15" t="n"/>
       <c r="O258" s="15" t="inlineStr">
         <is>
           <t>CÁMARA DOMO IP</t>
@@ -38032,11 +37048,7 @@
           <t>VIADUCTO SOBRE RÍO VINALOPÓ</t>
         </is>
       </c>
-      <c r="N259" s="15" t="inlineStr">
-        <is>
-          <t>454684</t>
-        </is>
-      </c>
+      <c r="N259" s="15" t="n"/>
       <c r="O259" s="15" t="inlineStr">
         <is>
           <t>CÁMARA DOMO IP</t>
@@ -38179,11 +37191,7 @@
           <t>VIADUCTO SOBRE CV-824 - SCVL-25A (BTS20A)</t>
         </is>
       </c>
-      <c r="N260" s="15" t="inlineStr">
-        <is>
-          <t>473530</t>
-        </is>
-      </c>
+      <c r="N260" s="15" t="n"/>
       <c r="O260" s="15" t="inlineStr">
         <is>
           <t>CÁMARA DOMO IP</t>
@@ -38326,11 +37334,7 @@
           <t>BTS 16A (2 FOR) (CT1 Túnel de Las Barrancadas)</t>
         </is>
       </c>
-      <c r="N261" s="15" t="inlineStr">
-        <is>
-          <t>444821</t>
-        </is>
-      </c>
+      <c r="N261" s="15" t="n"/>
       <c r="O261" s="15" t="inlineStr">
         <is>
           <t>CÁMARA DOMO IP</t>
@@ -38473,11 +37477,7 @@
           <t>BTS 19A - SCVL-24A</t>
         </is>
       </c>
-      <c r="N262" s="15" t="inlineStr">
-        <is>
-          <t>468144</t>
-        </is>
-      </c>
+      <c r="N262" s="15" t="n"/>
       <c r="O262" s="15" t="inlineStr">
         <is>
           <t>CÁMARA DOMO IP</t>
@@ -38796,11 +37796,7 @@
           <t>ATI 321.4</t>
         </is>
       </c>
-      <c r="N265" s="15" t="inlineStr">
-        <is>
-          <t>450660</t>
-        </is>
-      </c>
+      <c r="N265" s="15" t="n"/>
       <c r="O265" s="15" t="inlineStr">
         <is>
           <t>CÁMARA DOMO IP</t>
@@ -38943,11 +37939,7 @@
           <t>VIADUCTO SOBRE EL CORDEL DEL CAMINO DE SAX - SCVL-21</t>
         </is>
       </c>
-      <c r="N266" s="15" t="inlineStr">
-        <is>
-          <t>436290</t>
-        </is>
-      </c>
+      <c r="N266" s="15" t="n"/>
       <c r="O266" s="15" t="inlineStr">
         <is>
           <t>CÁMARA DOMO IP</t>
@@ -39090,11 +38082,7 @@
           <t>BASE DE MANTENIMIENTO MONFORTE DEL CID (NODO-3)</t>
         </is>
       </c>
-      <c r="N267" s="15" t="inlineStr">
-        <is>
-          <t>465134</t>
-        </is>
-      </c>
+      <c r="N267" s="15" t="n"/>
       <c r="O267" s="15" t="inlineStr">
         <is>
           <t>CÁMARA DOMO IP</t>
@@ -39237,11 +38225,7 @@
           <t>PÉRGOLA SOBRE VÍA ALICANTE-VILLENA</t>
         </is>
       </c>
-      <c r="N268" s="15" t="inlineStr">
-        <is>
-          <t>482404</t>
-        </is>
-      </c>
+      <c r="N268" s="15" t="n"/>
       <c r="O268" s="15" t="inlineStr">
         <is>
           <t>CÁMARA DOMO IP</t>
@@ -39384,11 +38368,7 @@
           <t>BTS 09B - DCC-4a</t>
         </is>
       </c>
-      <c r="N269" s="15" t="inlineStr">
-        <is>
-          <t>392925</t>
-        </is>
-      </c>
+      <c r="N269" s="15" t="n"/>
       <c r="O269" s="15" t="inlineStr">
         <is>
           <t>CÁMARA DOMO IP</t>
@@ -39531,11 +38511,7 @@
           <t>VIADUCTO SOBRE RAMBLA DEL SALITRE</t>
         </is>
       </c>
-      <c r="N270" s="15" t="inlineStr">
-        <is>
-          <t>453957</t>
-        </is>
-      </c>
+      <c r="N270" s="15" t="n"/>
       <c r="O270" s="15" t="inlineStr">
         <is>
           <t>CÁMARA DOMO IP</t>
@@ -39678,11 +38654,7 @@
           <t>BTS 22A (1 FOR + 3 FOR + 3 FOR-OP)</t>
         </is>
       </c>
-      <c r="N271" s="15" t="inlineStr">
-        <is>
-          <t>481682</t>
-        </is>
-      </c>
+      <c r="N271" s="15" t="n"/>
       <c r="O271" s="15" t="inlineStr">
         <is>
           <t>CÁMARA DOMO IP</t>
@@ -39825,11 +38797,7 @@
           <t>VIADUCTO SOBRE BARRANCO DE LOS BALADRES</t>
         </is>
       </c>
-      <c r="N272" s="15" t="inlineStr">
-        <is>
-          <t>457504</t>
-        </is>
-      </c>
+      <c r="N272" s="15" t="n"/>
       <c r="O272" s="15" t="inlineStr">
         <is>
           <t>CÁMARA DOMO IP</t>
@@ -40061,11 +39029,7 @@
           <t>Estación Villena</t>
         </is>
       </c>
-      <c r="N274" s="15" t="inlineStr">
-        <is>
-          <t>435487</t>
-        </is>
-      </c>
+      <c r="N274" s="15" t="n"/>
       <c r="O274" s="15" t="inlineStr">
         <is>
           <t>CÁMARA DOMO IP</t>
@@ -40208,11 +39172,7 @@
           <t>Estación Villena</t>
         </is>
       </c>
-      <c r="N275" s="15" t="inlineStr">
-        <is>
-          <t>435487</t>
-        </is>
-      </c>
+      <c r="N275" s="15" t="n"/>
       <c r="O275" s="15" t="inlineStr">
         <is>
           <t>CÁMARA DOMO IP</t>
@@ -40355,11 +39315,7 @@
           <t>BASE DE MANTENIMIENTO MONFORTE DEL CID (NODO-4)</t>
         </is>
       </c>
-      <c r="N276" s="15" t="inlineStr">
-        <is>
-          <t>465134</t>
-        </is>
-      </c>
+      <c r="N276" s="15" t="n"/>
       <c r="O276" s="15" t="inlineStr">
         <is>
           <t>CÁMARA DOMO IP</t>
@@ -40502,11 +39458,7 @@
           <t>TÚNEL DE LAS BARRANCADAS (2.856m) (boca Albacete)</t>
         </is>
       </c>
-      <c r="N277" s="15" t="inlineStr">
-        <is>
-          <t>444814</t>
-        </is>
-      </c>
+      <c r="N277" s="15" t="n"/>
       <c r="O277" s="15" t="inlineStr">
         <is>
           <t>CÁMARA DOMO IP</t>
@@ -40649,11 +39601,7 @@
           <t>ATI 312.2</t>
         </is>
       </c>
-      <c r="N278" s="15" t="inlineStr">
-        <is>
-          <t>355696</t>
-        </is>
-      </c>
+      <c r="N278" s="15" t="n"/>
       <c r="O278" s="15" t="inlineStr">
         <is>
           <t>CÁMARA DOMO IP</t>
@@ -40796,11 +39744,7 @@
           <t>TÚNEL V1 Nodo-2</t>
         </is>
       </c>
-      <c r="N279" s="15" t="inlineStr">
-        <is>
-          <t>483956</t>
-        </is>
-      </c>
+      <c r="N279" s="15" t="n"/>
       <c r="O279" s="15" t="inlineStr">
         <is>
           <t>CÁMARA DOMO IP</t>
@@ -40943,11 +39887,7 @@
           <t>BTS 17B</t>
         </is>
       </c>
-      <c r="N280" s="15" t="inlineStr">
-        <is>
-          <t>455432</t>
-        </is>
-      </c>
+      <c r="N280" s="15" t="n"/>
       <c r="O280" s="15" t="inlineStr">
         <is>
           <t>CÁMARA DOMO IP</t>
@@ -41090,11 +40030,7 @@
           <t>ET Bifurcación La Oliva (Nudo I)</t>
         </is>
       </c>
-      <c r="N281" s="15" t="inlineStr">
-        <is>
-          <t>410500</t>
-        </is>
-      </c>
+      <c r="N281" s="15" t="n"/>
       <c r="O281" s="15" t="inlineStr">
         <is>
           <t>CÁMARA DOMO IP</t>
@@ -41237,11 +40173,7 @@
           <t>Estación Villena</t>
         </is>
       </c>
-      <c r="N282" s="15" t="inlineStr">
-        <is>
-          <t>435487</t>
-        </is>
-      </c>
+      <c r="N282" s="15" t="n"/>
       <c r="O282" s="15" t="inlineStr">
         <is>
           <t>CÁMARA DOMO IP</t>
@@ -41384,11 +40316,7 @@
           <t>TÚNEL V2 Nodo-8</t>
         </is>
       </c>
-      <c r="N283" s="15" t="inlineStr">
-        <is>
-          <t>483956</t>
-        </is>
-      </c>
+      <c r="N283" s="15" t="n"/>
       <c r="O283" s="15" t="inlineStr">
         <is>
           <t>CÁMARA DOMO IP</t>
@@ -41616,11 +40544,7 @@
           <t>VIADUCTO AGOST</t>
         </is>
       </c>
-      <c r="N285" s="15" t="inlineStr">
-        <is>
-          <t>468669</t>
-        </is>
-      </c>
+      <c r="N285" s="15" t="n"/>
       <c r="O285" s="15" t="inlineStr">
         <is>
           <t>CÁMARA DOMO IP</t>
@@ -41763,11 +40687,7 @@
           <t>ATI 321.2</t>
         </is>
       </c>
-      <c r="N286" s="15" t="inlineStr">
-        <is>
-          <t>420421</t>
-        </is>
-      </c>
+      <c r="N286" s="15" t="n"/>
       <c r="O286" s="15" t="inlineStr">
         <is>
           <t>CÁMARA DOMO IP</t>
@@ -41910,11 +40830,7 @@
           <t>BTS 06B</t>
         </is>
       </c>
-      <c r="N287" s="15" t="inlineStr">
-        <is>
-          <t>371095</t>
-        </is>
-      </c>
+      <c r="N287" s="15" t="n"/>
       <c r="O287" s="15" t="inlineStr">
         <is>
           <t>CÁMARA DOMO IP</t>
@@ -42057,11 +40973,7 @@
           <t>BTS02A</t>
         </is>
       </c>
-      <c r="N288" s="15" t="inlineStr">
-        <is>
-          <t>332665</t>
-        </is>
-      </c>
+      <c r="N288" s="15" t="n"/>
       <c r="O288" s="15" t="inlineStr">
         <is>
           <t>CÁMARA DOMO IP</t>
@@ -42204,11 +41116,7 @@
           <t>BASE DE MANTENIMIENTO MONFORTE DEL CID (NODO-5)</t>
         </is>
       </c>
-      <c r="N289" s="15" t="inlineStr">
-        <is>
-          <t>465134</t>
-        </is>
-      </c>
+      <c r="N289" s="15" t="n"/>
       <c r="O289" s="15" t="inlineStr">
         <is>
           <t>CÁMARA DOMO IP</t>
@@ -42351,11 +41259,7 @@
           <t>TÚNEL V1 Nodo-5</t>
         </is>
       </c>
-      <c r="N290" s="15" t="inlineStr">
-        <is>
-          <t>483956</t>
-        </is>
-      </c>
+      <c r="N290" s="15" t="n"/>
       <c r="O290" s="15" t="inlineStr">
         <is>
           <t>CÁMARA DOMO IP</t>
@@ -42498,11 +41402,7 @@
           <t>Estación Villena</t>
         </is>
       </c>
-      <c r="N291" s="15" t="inlineStr">
-        <is>
-          <t>435487</t>
-        </is>
-      </c>
+      <c r="N291" s="15" t="n"/>
       <c r="O291" s="15" t="inlineStr">
         <is>
           <t>CÁMARA DOMO IP</t>
@@ -42645,11 +41545,7 @@
           <t>VIADUCTO SOBRE ACEQUIA DEL REY</t>
         </is>
       </c>
-      <c r="N292" s="15" t="inlineStr">
-        <is>
-          <t>431647</t>
-        </is>
-      </c>
+      <c r="N292" s="15" t="n"/>
       <c r="O292" s="15" t="inlineStr">
         <is>
           <t>CÁMARA DOMO IP</t>
@@ -42792,11 +41688,7 @@
           <t>TÚNEL DE LA SIERRA DE LAS ÁGUILAS (1.227m) (boca Albacete</t>
         </is>
       </c>
-      <c r="N293" s="15" t="inlineStr">
-        <is>
-          <t>470962</t>
-        </is>
-      </c>
+      <c r="N293" s="15" t="n"/>
       <c r="O293" s="15" t="inlineStr">
         <is>
           <t>CÁMARA DOMO IP</t>
@@ -42939,11 +41831,7 @@
           <t>ATI 312.3</t>
         </is>
       </c>
-      <c r="N294" s="15" t="inlineStr">
-        <is>
-          <t>365625</t>
-        </is>
-      </c>
+      <c r="N294" s="15" t="n"/>
       <c r="O294" s="15" t="inlineStr">
         <is>
           <t>CÁMARA DOMO IP</t>
@@ -43086,11 +41974,7 @@
           <t>TÚNEL V2 Nodo-12</t>
         </is>
       </c>
-      <c r="N295" s="15" t="inlineStr">
-        <is>
-          <t>483956</t>
-        </is>
-      </c>
+      <c r="N295" s="15" t="n"/>
       <c r="O295" s="15" t="inlineStr">
         <is>
           <t>CÁMARA DOMO IP</t>
@@ -43233,11 +42117,7 @@
           <t>BTS 10B</t>
         </is>
       </c>
-      <c r="N296" s="15" t="inlineStr">
-        <is>
-          <t>401577</t>
-        </is>
-      </c>
+      <c r="N296" s="15" t="n"/>
       <c r="O296" s="15" t="inlineStr">
         <is>
           <t>CÁMARA DOMO IP</t>
@@ -43380,11 +42260,7 @@
           <t>VIADUCTO 2 EL HONDO - SCVL-16A (BTS09B)</t>
         </is>
       </c>
-      <c r="N297" s="15" t="inlineStr">
-        <is>
-          <t>393795</t>
-        </is>
-      </c>
+      <c r="N297" s="15" t="n"/>
       <c r="O297" s="15" t="inlineStr">
         <is>
           <t>CÁMARA DOMO IP</t>
@@ -43527,11 +42403,7 @@
           <t>ET PAET Villena AV</t>
         </is>
       </c>
-      <c r="N298" s="15" t="inlineStr">
-        <is>
-          <t>435487</t>
-        </is>
-      </c>
+      <c r="N298" s="15" t="n"/>
       <c r="O298" s="15" t="inlineStr">
         <is>
           <t>CÁMARA DOMO IP</t>
@@ -43674,11 +42546,7 @@
           <t>ATI 312.5</t>
         </is>
       </c>
-      <c r="N299" s="15" t="inlineStr">
-        <is>
-          <t>398537</t>
-        </is>
-      </c>
+      <c r="N299" s="15" t="n"/>
       <c r="O299" s="15" t="inlineStr">
         <is>
           <t>CÁMARA DOMO IP</t>
@@ -43821,11 +42689,7 @@
           <t>BTS 21A</t>
         </is>
       </c>
-      <c r="N300" s="15" t="inlineStr">
-        <is>
-          <t>477939</t>
-        </is>
-      </c>
+      <c r="N300" s="15" t="n"/>
       <c r="O300" s="15" t="inlineStr">
         <is>
           <t>CÁMARA DOMO IP</t>
@@ -43968,11 +42832,7 @@
           <t>BTS02B</t>
         </is>
       </c>
-      <c r="N301" s="15" t="inlineStr">
-        <is>
-          <t>337647</t>
-        </is>
-      </c>
+      <c r="N301" s="15" t="n"/>
       <c r="O301" s="15" t="inlineStr">
         <is>
           <t>CÁMARA DOMO IP</t>
@@ -44293,11 +43153,7 @@
           <t>Estación Villena</t>
         </is>
       </c>
-      <c r="N304" s="15" t="inlineStr">
-        <is>
-          <t>435487</t>
-        </is>
-      </c>
+      <c r="N304" s="15" t="n"/>
       <c r="O304" s="15" t="inlineStr">
         <is>
           <t>CÁMARA DOMO IP</t>
@@ -44440,11 +43296,7 @@
           <t>BASE DE MANTENIMIENTO MONFORTE DEL CID (NODO-6)</t>
         </is>
       </c>
-      <c r="N305" s="15" t="inlineStr">
-        <is>
-          <t>465134</t>
-        </is>
-      </c>
+      <c r="N305" s="15" t="n"/>
       <c r="O305" s="15" t="inlineStr">
         <is>
           <t>CÁMARA DOMO IP</t>
@@ -44587,11 +43439,7 @@
           <t>Estación Villena</t>
         </is>
       </c>
-      <c r="N306" s="15" t="inlineStr">
-        <is>
-          <t>435487</t>
-        </is>
-      </c>
+      <c r="N306" s="15" t="n"/>
       <c r="O306" s="15" t="inlineStr">
         <is>
           <t>CÁMARA DOMO IP</t>
@@ -44734,11 +43582,7 @@
           <t>BTS 09A - SCVL-15A</t>
         </is>
       </c>
-      <c r="N307" s="15" t="inlineStr">
-        <is>
-          <t>388527</t>
-        </is>
-      </c>
+      <c r="N307" s="15" t="n"/>
       <c r="O307" s="15" t="inlineStr">
         <is>
           <t>CÁMARA DOMO IP</t>
@@ -44881,11 +43725,7 @@
           <t>Estación Villena</t>
         </is>
       </c>
-      <c r="N308" s="15" t="inlineStr">
-        <is>
-          <t>435487</t>
-        </is>
-      </c>
+      <c r="N308" s="15" t="n"/>
       <c r="O308" s="15" t="inlineStr">
         <is>
           <t>CÁMARA DOMO IP</t>
@@ -45028,11 +43868,7 @@
           <t>BTS 19B (1 FOR + 3 FOR-OP) DCC-6a en PK470+600</t>
         </is>
       </c>
-      <c r="N309" s="15" t="inlineStr">
-        <is>
-          <t>470416</t>
-        </is>
-      </c>
+      <c r="N309" s="15" t="n"/>
       <c r="O309" s="15" t="inlineStr">
         <is>
           <t>CÁMARA DOMO IP</t>
@@ -45175,11 +44011,7 @@
           <t>Estación Villena</t>
         </is>
       </c>
-      <c r="N310" s="15" t="inlineStr">
-        <is>
-          <t>435487</t>
-        </is>
-      </c>
+      <c r="N310" s="15" t="n"/>
       <c r="O310" s="15" t="inlineStr">
         <is>
           <t>CÁMARA DOMO IP</t>
@@ -45322,11 +44154,7 @@
           <t>ET Alacant-Terminal</t>
         </is>
       </c>
-      <c r="N311" s="15" t="inlineStr">
-        <is>
-          <t>483925</t>
-        </is>
-      </c>
+      <c r="N311" s="15" t="n"/>
       <c r="O311" s="15" t="inlineStr">
         <is>
           <t>CÁMARA DOMO IP</t>
@@ -45469,11 +44297,7 @@
           <t>BTS 08B</t>
         </is>
       </c>
-      <c r="N312" s="15" t="inlineStr">
-        <is>
-          <t>385743</t>
-        </is>
-      </c>
+      <c r="N312" s="15" t="n"/>
       <c r="O312" s="15" t="inlineStr">
         <is>
           <t>CÁMARA DOMO IP</t>
@@ -45616,11 +44440,7 @@
           <t>TÚNEL DE LAS BARRANCADAS (2.856m) (boca Alicante)</t>
         </is>
       </c>
-      <c r="N313" s="15" t="inlineStr">
-        <is>
-          <t>444814</t>
-        </is>
-      </c>
+      <c r="N313" s="15" t="n"/>
       <c r="O313" s="15" t="inlineStr">
         <is>
           <t>CÁMARA DOMO IP</t>
@@ -45763,11 +44583,7 @@
           <t>BTS 18A - SCVL-23A</t>
         </is>
       </c>
-      <c r="N314" s="15" t="inlineStr">
-        <is>
-          <t>459390</t>
-        </is>
-      </c>
+      <c r="N314" s="15" t="n"/>
       <c r="O314" s="15" t="inlineStr">
         <is>
           <t>CÁMARA DOMO IP</t>
@@ -45910,11 +44726,7 @@
           <t>Estación Villena</t>
         </is>
       </c>
-      <c r="N315" s="15" t="inlineStr">
-        <is>
-          <t>435487</t>
-        </is>
-      </c>
+      <c r="N315" s="15" t="n"/>
       <c r="O315" s="15" t="inlineStr">
         <is>
           <t>CÁMARA DOMO IP</t>
@@ -46057,11 +44869,7 @@
           <t>TÚNEL DE LA SERRETA (301m) (boca Alicante)</t>
         </is>
       </c>
-      <c r="N316" s="15" t="inlineStr">
-        <is>
-          <t>480174</t>
-        </is>
-      </c>
+      <c r="N316" s="15" t="n"/>
       <c r="O316" s="15" t="inlineStr">
         <is>
           <t>CÁMARA DOMO IP</t>
@@ -46204,11 +45012,7 @@
           <t>BASE DE MANTENIMIENTO MONFORTE DEL CID (NODO-8)</t>
         </is>
       </c>
-      <c r="N317" s="15" t="inlineStr">
-        <is>
-          <t>465134</t>
-        </is>
-      </c>
+      <c r="N317" s="15" t="n"/>
       <c r="O317" s="15" t="inlineStr">
         <is>
           <t>CÁMARA DOMO IP</t>
@@ -46351,11 +45155,7 @@
           <t>VIADUCTO SOBRE FFCC LA ENCINA-ALICANTE</t>
         </is>
       </c>
-      <c r="N318" s="15" t="inlineStr">
-        <is>
-          <t>455844</t>
-        </is>
-      </c>
+      <c r="N318" s="15" t="n"/>
       <c r="O318" s="15" t="inlineStr">
         <is>
           <t>CÁMARA DOMO IP</t>
@@ -46498,11 +45298,7 @@
           <t>BTS 07B</t>
         </is>
       </c>
-      <c r="N319" s="15" t="inlineStr">
-        <is>
-          <t>376881</t>
-        </is>
-      </c>
+      <c r="N319" s="15" t="n"/>
       <c r="O319" s="15" t="inlineStr">
         <is>
           <t>CÁMARA DOMO IP</t>
@@ -46645,11 +45441,7 @@
           <t>BTS 11B</t>
         </is>
       </c>
-      <c r="N320" s="15" t="inlineStr">
-        <is>
-          <t>410070</t>
-        </is>
-      </c>
+      <c r="N320" s="15" t="n"/>
       <c r="O320" s="15" t="inlineStr">
         <is>
           <t>CÁMARA DOMO IP</t>
@@ -46792,11 +45584,7 @@
           <t>BTS 04A</t>
         </is>
       </c>
-      <c r="N321" s="15" t="inlineStr">
-        <is>
-          <t>351720</t>
-        </is>
-      </c>
+      <c r="N321" s="15" t="n"/>
       <c r="O321" s="15" t="inlineStr">
         <is>
           <t>CÁMARA DOMO IP</t>
@@ -47028,11 +45816,7 @@
           <t>BTS 11B</t>
         </is>
       </c>
-      <c r="N323" s="15" t="inlineStr">
-        <is>
-          <t>410070</t>
-        </is>
-      </c>
+      <c r="N323" s="15" t="n"/>
       <c r="O323" s="15" t="inlineStr">
         <is>
           <t>CÁMARA DOMO IP</t>
@@ -47175,11 +45959,7 @@
           <t>BTS 14A</t>
         </is>
       </c>
-      <c r="N324" s="15" t="inlineStr">
-        <is>
-          <t>429835</t>
-        </is>
-      </c>
+      <c r="N324" s="15" t="n"/>
       <c r="O324" s="15" t="inlineStr">
         <is>
           <t>CÁMARA DOMO IP</t>
@@ -47411,11 +46191,7 @@
           <t>TÚNEL DE ACCESO ALICANTE (1.067m) (boca Albacete)</t>
         </is>
       </c>
-      <c r="N326" s="15" t="inlineStr">
-        <is>
-          <t>483956</t>
-        </is>
-      </c>
+      <c r="N326" s="15" t="n"/>
       <c r="O326" s="15" t="inlineStr">
         <is>
           <t>CÁMARA DOMO IP</t>
@@ -47558,11 +46334,7 @@
           <t>TÚNEL V1 Nodo-4</t>
         </is>
       </c>
-      <c r="N327" s="15" t="inlineStr">
-        <is>
-          <t>483956</t>
-        </is>
-      </c>
+      <c r="N327" s="15" t="n"/>
       <c r="O327" s="15" t="inlineStr">
         <is>
           <t>CÁMARA DOMO IP</t>
@@ -47705,11 +46477,7 @@
           <t>BTS 13A</t>
         </is>
       </c>
-      <c r="N328" s="15" t="inlineStr">
-        <is>
-          <t>421704</t>
-        </is>
-      </c>
+      <c r="N328" s="15" t="n"/>
       <c r="O328" s="15" t="inlineStr">
         <is>
           <t>CÁMARA DOMO IP</t>
@@ -47852,11 +46620,7 @@
           <t>BTS 07A - SCVL-13A</t>
         </is>
       </c>
-      <c r="N329" s="15" t="inlineStr">
-        <is>
-          <t>374756</t>
-        </is>
-      </c>
+      <c r="N329" s="15" t="n"/>
       <c r="O329" s="15" t="inlineStr">
         <is>
           <t>CÁMARA DOMO IP</t>
@@ -47999,11 +46763,7 @@
           <t>VIADUCTO - SCVL-14A (BTS08A)</t>
         </is>
       </c>
-      <c r="N330" s="15" t="inlineStr">
-        <is>
-          <t>382592</t>
-        </is>
-      </c>
+      <c r="N330" s="15" t="n"/>
       <c r="O330" s="15" t="inlineStr">
         <is>
           <t>CÁMARA DOMO IP</t>
@@ -48146,11 +46906,7 @@
           <t>BTS 20A (1 FOR) (CT 4 Túnel de la Sierra de Las Águilas)</t>
         </is>
       </c>
-      <c r="N331" s="15" t="inlineStr">
-        <is>
-          <t>472389</t>
-        </is>
-      </c>
+      <c r="N331" s="15" t="n"/>
       <c r="O331" s="15" t="inlineStr">
         <is>
           <t>CÁMARA DOMO IP</t>
@@ -48293,11 +47049,7 @@
           <t>ATF 312.1</t>
         </is>
       </c>
-      <c r="N332" s="15" t="inlineStr">
-        <is>
-          <t>342890</t>
-        </is>
-      </c>
+      <c r="N332" s="15" t="n"/>
       <c r="O332" s="15" t="inlineStr">
         <is>
           <t>CÁMARA DOMO IP</t>
@@ -48440,11 +47192,7 @@
           <t>BTS 12B</t>
         </is>
       </c>
-      <c r="N333" s="15" t="inlineStr">
-        <is>
-          <t>417468</t>
-        </is>
-      </c>
+      <c r="N333" s="15" t="n"/>
       <c r="O333" s="15" t="inlineStr">
         <is>
           <t>CÁMARA DOMO IP</t>
@@ -48587,11 +47335,7 @@
           <t>BTS 12A - SCVL-18A</t>
         </is>
       </c>
-      <c r="N334" s="15" t="inlineStr">
-        <is>
-          <t>413835</t>
-        </is>
-      </c>
+      <c r="N334" s="15" t="n"/>
       <c r="O334" s="15" t="inlineStr">
         <is>
           <t>CÁMARA DOMO IP</t>
@@ -48734,11 +47478,7 @@
           <t>PICV 442 - DCC-5a</t>
         </is>
       </c>
-      <c r="N335" s="15" t="inlineStr">
-        <is>
-          <t>442266</t>
-        </is>
-      </c>
+      <c r="N335" s="15" t="n"/>
       <c r="O335" s="15" t="inlineStr">
         <is>
           <t>CÁMARA FIJA IP</t>
@@ -48881,11 +47621,7 @@
           <t>PS 401,5 a</t>
         </is>
       </c>
-      <c r="N336" s="15" t="inlineStr">
-        <is>
-          <t>401522</t>
-        </is>
-      </c>
+      <c r="N336" s="15" t="n"/>
       <c r="O336" s="15" t="inlineStr">
         <is>
           <t>CÁMARA FIJA IP</t>
@@ -49028,11 +47764,7 @@
           <t>ATF 321.1</t>
         </is>
       </c>
-      <c r="N337" s="15" t="inlineStr">
-        <is>
-          <t>405999</t>
-        </is>
-      </c>
+      <c r="N337" s="15" t="n"/>
       <c r="O337" s="15" t="inlineStr">
         <is>
           <t>CÁMARA FIJA IP</t>
@@ -49175,11 +47907,7 @@
           <t>Estación Villena</t>
         </is>
       </c>
-      <c r="N338" s="15" t="inlineStr">
-        <is>
-          <t>435487</t>
-        </is>
-      </c>
+      <c r="N338" s="15" t="n"/>
       <c r="O338" s="15" t="inlineStr">
         <is>
           <t>CÁMARA FIJA IP</t>
@@ -49322,11 +48050,7 @@
           <t>PS 390,2 a</t>
         </is>
       </c>
-      <c r="N339" s="15" t="inlineStr">
-        <is>
-          <t>390204</t>
-        </is>
-      </c>
+      <c r="N339" s="15" t="n"/>
       <c r="O339" s="15" t="inlineStr">
         <is>
           <t>CÁMARA FIJA IP</t>
@@ -49469,11 +48193,7 @@
           <t>PS 370,0 a</t>
         </is>
       </c>
-      <c r="N340" s="15" t="inlineStr">
-        <is>
-          <t>370069</t>
-        </is>
-      </c>
+      <c r="N340" s="15" t="n"/>
       <c r="O340" s="15" t="inlineStr">
         <is>
           <t>CÁMARA FIJA IP</t>
@@ -49616,11 +48336,7 @@
           <t>SE 312 - SUBESTACIÓN ELÉCTRICA CAMPANARIO</t>
         </is>
       </c>
-      <c r="N341" s="15" t="inlineStr">
-        <is>
-          <t>378076</t>
-        </is>
-      </c>
+      <c r="N341" s="15" t="n"/>
       <c r="O341" s="15" t="inlineStr">
         <is>
           <t>CÁMARA FIJA IP</t>
@@ -49763,11 +48479,7 @@
           <t>ATF 321.1</t>
         </is>
       </c>
-      <c r="N342" s="15" t="inlineStr">
-        <is>
-          <t>405999</t>
-        </is>
-      </c>
+      <c r="N342" s="15" t="n"/>
       <c r="O342" s="15" t="inlineStr">
         <is>
           <t>CÁMARA FIJA IP</t>
@@ -49910,11 +48622,7 @@
           <t>ET PAET BONETE AV (MTO UTE)</t>
         </is>
       </c>
-      <c r="N343" s="15" t="inlineStr">
-        <is>
-          <t>373493</t>
-        </is>
-      </c>
+      <c r="N343" s="15" t="n"/>
       <c r="O343" s="15" t="inlineStr">
         <is>
           <t>CÁMARA FIJA IP</t>
@@ -50057,11 +48765,7 @@
           <t>PS 477,0 a</t>
         </is>
       </c>
-      <c r="N344" s="15" t="inlineStr">
-        <is>
-          <t>477024</t>
-        </is>
-      </c>
+      <c r="N344" s="15" t="n"/>
       <c r="O344" s="15" t="inlineStr">
         <is>
           <t>CÁMARA FIJA IP</t>
@@ -50204,11 +48908,7 @@
           <t>ET PAET BONETE AV (MTO UTE)</t>
         </is>
       </c>
-      <c r="N345" s="15" t="inlineStr">
-        <is>
-          <t>373493</t>
-        </is>
-      </c>
+      <c r="N345" s="15" t="n"/>
       <c r="O345" s="15" t="inlineStr">
         <is>
           <t>CÁMARA FIJA IP</t>
@@ -50351,11 +49051,7 @@
           <t>ET PAET BONETE AV (MTO UTE)</t>
         </is>
       </c>
-      <c r="N346" s="15" t="inlineStr">
-        <is>
-          <t>373493</t>
-        </is>
-      </c>
+      <c r="N346" s="15" t="n"/>
       <c r="O346" s="15" t="inlineStr">
         <is>
           <t>CÁMARA FIJA IP</t>
@@ -50498,11 +49194,7 @@
           <t>PS 321,8a (PS 322,0a)</t>
         </is>
       </c>
-      <c r="N347" s="15" t="inlineStr">
-        <is>
-          <t>321784</t>
-        </is>
-      </c>
+      <c r="N347" s="15" t="n"/>
       <c r="O347" s="15" t="inlineStr">
         <is>
           <t>CÁMARA FIJA IP</t>
@@ -50645,11 +49337,7 @@
           <t>VIADUCTO SOBRE RAMBLA DEL SALITRE</t>
         </is>
       </c>
-      <c r="N348" s="15" t="inlineStr">
-        <is>
-          <t>453957</t>
-        </is>
-      </c>
+      <c r="N348" s="15" t="n"/>
       <c r="O348" s="15" t="inlineStr">
         <is>
           <t>CÁMARA FIJA IP</t>
@@ -50792,11 +49480,7 @@
           <t>ET PAET MONFORTE DEL CID AV (MTO UTE)</t>
         </is>
       </c>
-      <c r="N349" s="15" t="inlineStr">
-        <is>
-          <t>464685</t>
-        </is>
-      </c>
+      <c r="N349" s="15" t="n"/>
       <c r="O349" s="15" t="inlineStr">
         <is>
           <t>CÁMARA FIJA IP</t>
@@ -50939,11 +49623,7 @@
           <t>PS 344,9 a</t>
         </is>
       </c>
-      <c r="N350" s="15" t="inlineStr">
-        <is>
-          <t>344986</t>
-        </is>
-      </c>
+      <c r="N350" s="15" t="n"/>
       <c r="O350" s="15" t="inlineStr">
         <is>
           <t>CÁMARA FIJA IP</t>
@@ -51086,11 +49766,7 @@
           <t>ET PAET MONFORTE DEL CID AV (MTO UTE)</t>
         </is>
       </c>
-      <c r="N351" s="15" t="inlineStr">
-        <is>
-          <t>464685</t>
-        </is>
-      </c>
+      <c r="N351" s="15" t="n"/>
       <c r="O351" s="15" t="inlineStr">
         <is>
           <t>CÁMARA FIJA IP</t>
@@ -51233,11 +49909,7 @@
           <t>PS 410,0 a</t>
         </is>
       </c>
-      <c r="N352" s="15" t="inlineStr">
-        <is>
-          <t>410086</t>
-        </is>
-      </c>
+      <c r="N352" s="15" t="n"/>
       <c r="O352" s="15" t="inlineStr">
         <is>
           <t>CÁMARA FIJA IP</t>
@@ -51380,11 +50052,7 @@
           <t>PS 480,1 a</t>
         </is>
       </c>
-      <c r="N353" s="15" t="inlineStr">
-        <is>
-          <t>480102</t>
-        </is>
-      </c>
+      <c r="N353" s="15" t="n"/>
       <c r="O353" s="15" t="inlineStr">
         <is>
           <t>CÁMARA FIJA IP</t>
@@ -51527,11 +50195,7 @@
           <t>PS 478,1 a</t>
         </is>
       </c>
-      <c r="N354" s="15" t="inlineStr">
-        <is>
-          <t>478169</t>
-        </is>
-      </c>
+      <c r="N354" s="15" t="n"/>
       <c r="O354" s="15" t="inlineStr">
         <is>
           <t>CÁMARA FIJA IP</t>
@@ -51674,11 +50338,7 @@
           <t>ET PAET Chinchilla AV</t>
         </is>
       </c>
-      <c r="N355" s="15" t="inlineStr">
-        <is>
-          <t>336566</t>
-        </is>
-      </c>
+      <c r="N355" s="15" t="n"/>
       <c r="O355" s="15" t="inlineStr">
         <is>
           <t>CÁMARA FIJA IP</t>
@@ -51821,11 +50481,7 @@
           <t>ET PAET MONFORTE DEL CID AV (MTO UTE)</t>
         </is>
       </c>
-      <c r="N356" s="15" t="inlineStr">
-        <is>
-          <t>464685</t>
-        </is>
-      </c>
+      <c r="N356" s="15" t="n"/>
       <c r="O356" s="15" t="inlineStr">
         <is>
           <t>CÁMARA FIJA IP</t>
@@ -51968,11 +50624,7 @@
           <t>PS 440,2 a</t>
         </is>
       </c>
-      <c r="N357" s="15" t="inlineStr">
-        <is>
-          <t>440258</t>
-        </is>
-      </c>
+      <c r="N357" s="15" t="n"/>
       <c r="O357" s="15" t="inlineStr">
         <is>
           <t>CÁMARA FIJA IP</t>
@@ -52115,11 +50767,7 @@
           <t>Bifurcación Vinalopo</t>
         </is>
       </c>
-      <c r="N358" s="15" t="inlineStr">
-        <is>
-          <t>464480</t>
-        </is>
-      </c>
+      <c r="N358" s="15" t="n"/>
       <c r="O358" s="15" t="inlineStr">
         <is>
           <t>CÁMARA FIJA IP</t>
@@ -52262,11 +50910,7 @@
           <t>ATI 321.7</t>
         </is>
       </c>
-      <c r="N359" s="15" t="inlineStr">
-        <is>
-          <t>481640</t>
-        </is>
-      </c>
+      <c r="N359" s="15" t="n"/>
       <c r="O359" s="15" t="inlineStr">
         <is>
           <t>CÁMARA FIJA IP</t>
@@ -52409,11 +51053,7 @@
           <t>ET PAET BONETE AV (MTO UTE)</t>
         </is>
       </c>
-      <c r="N360" s="15" t="inlineStr">
-        <is>
-          <t>373493</t>
-        </is>
-      </c>
+      <c r="N360" s="15" t="n"/>
       <c r="O360" s="15" t="inlineStr">
         <is>
           <t>CÁMARA FIJA IP</t>
@@ -52556,11 +51196,7 @@
           <t>PB Caudete AV</t>
         </is>
       </c>
-      <c r="N361" s="15" t="inlineStr">
-        <is>
-          <t>425227</t>
-        </is>
-      </c>
+      <c r="N361" s="15" t="n"/>
       <c r="O361" s="15" t="inlineStr">
         <is>
           <t>CÁMARA FIJA IP</t>
@@ -52703,11 +51339,7 @@
           <t>ET PAET MONFORTE DEL CID AV (MTO UTE)</t>
         </is>
       </c>
-      <c r="N362" s="15" t="inlineStr">
-        <is>
-          <t>464685</t>
-        </is>
-      </c>
+      <c r="N362" s="15" t="n"/>
       <c r="O362" s="15" t="inlineStr">
         <is>
           <t>CÁMARA FIJA IP</t>
@@ -52850,11 +51482,7 @@
           <t>BASE DE MANTENIMIENTO MONFORTE DEL CID (NODO-7 NAV</t>
         </is>
       </c>
-      <c r="N363" s="15" t="inlineStr">
-        <is>
-          <t>465134</t>
-        </is>
-      </c>
+      <c r="N363" s="15" t="n"/>
       <c r="O363" s="15" t="inlineStr">
         <is>
           <t>CÁMARA FIJA IP</t>
@@ -52997,11 +51625,7 @@
           <t>ATI 321.3</t>
         </is>
       </c>
-      <c r="N364" s="15" t="inlineStr">
-        <is>
-          <t>429607</t>
-        </is>
-      </c>
+      <c r="N364" s="15" t="n"/>
       <c r="O364" s="15" t="inlineStr">
         <is>
           <t>CÁMARA FIJA IP</t>
@@ -53144,11 +51768,7 @@
           <t>ET PAET MONFORTE DEL CID AV (MTO UTE)</t>
         </is>
       </c>
-      <c r="N365" s="15" t="inlineStr">
-        <is>
-          <t>464685</t>
-        </is>
-      </c>
+      <c r="N365" s="15" t="n"/>
       <c r="O365" s="15" t="inlineStr">
         <is>
           <t>CÁMARA FIJA IP</t>
@@ -53291,11 +51911,7 @@
           <t>PS 477,9 a</t>
         </is>
       </c>
-      <c r="N366" s="15" t="inlineStr">
-        <is>
-          <t>477981</t>
-        </is>
-      </c>
+      <c r="N366" s="15" t="n"/>
       <c r="O366" s="15" t="inlineStr">
         <is>
           <t>CÁMARA FIJA IP</t>
@@ -53438,11 +52054,7 @@
           <t>ET Bifurcación La Oliva (Nudo I)</t>
         </is>
       </c>
-      <c r="N367" s="15" t="inlineStr">
-        <is>
-          <t>410500</t>
-        </is>
-      </c>
+      <c r="N367" s="15" t="n"/>
       <c r="O367" s="15" t="inlineStr">
         <is>
           <t>CÁMARA MINIDOMO IP</t>
@@ -53585,11 +52197,7 @@
           <t>Estación Villena</t>
         </is>
       </c>
-      <c r="N368" s="15" t="inlineStr">
-        <is>
-          <t>435487</t>
-        </is>
-      </c>
+      <c r="N368" s="15" t="n"/>
       <c r="O368" s="15" t="inlineStr">
         <is>
           <t>CÁMARA MINIDOMO IP</t>
@@ -53732,11 +52340,7 @@
           <t>Estación Villena</t>
         </is>
       </c>
-      <c r="N369" s="15" t="inlineStr">
-        <is>
-          <t>435487</t>
-        </is>
-      </c>
+      <c r="N369" s="15" t="n"/>
       <c r="O369" s="15" t="inlineStr">
         <is>
           <t>CÁMARA MINIDOMO IP</t>
@@ -53879,11 +52483,7 @@
           <t>ATI 321.2</t>
         </is>
       </c>
-      <c r="N370" s="15" t="inlineStr">
-        <is>
-          <t>420421</t>
-        </is>
-      </c>
+      <c r="N370" s="15" t="n"/>
       <c r="O370" s="15" t="inlineStr">
         <is>
           <t>CÁMARA MINIDOMO IP</t>
@@ -54026,11 +52626,7 @@
           <t>ET PAET Villena AV</t>
         </is>
       </c>
-      <c r="N371" s="15" t="inlineStr">
-        <is>
-          <t>435487</t>
-        </is>
-      </c>
+      <c r="N371" s="15" t="n"/>
       <c r="O371" s="15" t="inlineStr">
         <is>
           <t>CÁMARA MINIDOMO IP</t>
@@ -54173,11 +52769,7 @@
           <t>Estación Villena</t>
         </is>
       </c>
-      <c r="N372" s="15" t="inlineStr">
-        <is>
-          <t>435487</t>
-        </is>
-      </c>
+      <c r="N372" s="15" t="n"/>
       <c r="O372" s="15" t="inlineStr">
         <is>
           <t>CÁMARA MINIDOMO IP</t>
@@ -54320,11 +52912,7 @@
           <t>ATF 312.1</t>
         </is>
       </c>
-      <c r="N373" s="15" t="inlineStr">
-        <is>
-          <t>342890</t>
-        </is>
-      </c>
+      <c r="N373" s="15" t="n"/>
       <c r="O373" s="15" t="inlineStr">
         <is>
           <t>CÁMARA MINIDOMO IP</t>
@@ -54467,11 +53055,7 @@
           <t>ATI 312.2</t>
         </is>
       </c>
-      <c r="N374" s="15" t="inlineStr">
-        <is>
-          <t>355696</t>
-        </is>
-      </c>
+      <c r="N374" s="15" t="n"/>
       <c r="O374" s="15" t="inlineStr">
         <is>
           <t>CÁMARA MINIDOMO IP</t>
@@ -54614,11 +53198,7 @@
           <t>ATI 321.4</t>
         </is>
       </c>
-      <c r="N375" s="15" t="inlineStr">
-        <is>
-          <t>450660</t>
-        </is>
-      </c>
+      <c r="N375" s="15" t="n"/>
       <c r="O375" s="15" t="inlineStr">
         <is>
           <t>CÁMARA MINIDOMO IP</t>
@@ -54761,11 +53341,7 @@
           <t>SE 312 - SUBESTACIÓN ELÉCTRICA CAMPANARIO</t>
         </is>
       </c>
-      <c r="N376" s="15" t="inlineStr">
-        <is>
-          <t>378076</t>
-        </is>
-      </c>
+      <c r="N376" s="15" t="n"/>
       <c r="O376" s="15" t="inlineStr">
         <is>
           <t>CÁMARA MINIDOMO IP</t>
@@ -54908,11 +53484,7 @@
           <t>Estación Villena</t>
         </is>
       </c>
-      <c r="N377" s="15" t="inlineStr">
-        <is>
-          <t>435487</t>
-        </is>
-      </c>
+      <c r="N377" s="15" t="n"/>
       <c r="O377" s="15" t="inlineStr">
         <is>
           <t>CÁMARA MINIDOMO IP</t>
@@ -55055,11 +53627,7 @@
           <t>ET PAET MONFORTE DEL CID AV (MTO UTE)</t>
         </is>
       </c>
-      <c r="N378" s="15" t="inlineStr">
-        <is>
-          <t>464685</t>
-        </is>
-      </c>
+      <c r="N378" s="15" t="n"/>
       <c r="O378" s="15" t="inlineStr">
         <is>
           <t>CÁMARA MINIDOMO IP</t>
@@ -55202,11 +53770,7 @@
           <t>ET PAET Villena AV</t>
         </is>
       </c>
-      <c r="N379" s="15" t="inlineStr">
-        <is>
-          <t>435487</t>
-        </is>
-      </c>
+      <c r="N379" s="15" t="n"/>
       <c r="O379" s="15" t="inlineStr">
         <is>
           <t>CÁMARA MINIDOMO IP</t>
@@ -55349,11 +53913,7 @@
           <t>ATI 321.6</t>
         </is>
       </c>
-      <c r="N380" s="15" t="inlineStr">
-        <is>
-          <t>474060</t>
-        </is>
-      </c>
+      <c r="N380" s="15" t="n"/>
       <c r="O380" s="15" t="inlineStr">
         <is>
           <t>CÁMARA MINIDOMO IP</t>
@@ -55496,11 +54056,7 @@
           <t>GALERÍA EVACUACIÓN DEL TÚNEL DE ACCESO ALICANTE</t>
         </is>
       </c>
-      <c r="N381" s="15" t="inlineStr">
-        <is>
-          <t>483956</t>
-        </is>
-      </c>
+      <c r="N381" s="15" t="n"/>
       <c r="O381" s="15" t="inlineStr">
         <is>
           <t>CÁMARA MINIDOMO IP</t>
@@ -55643,11 +54199,7 @@
           <t>ATI 312.5</t>
         </is>
       </c>
-      <c r="N382" s="15" t="inlineStr">
-        <is>
-          <t>398537</t>
-        </is>
-      </c>
+      <c r="N382" s="15" t="n"/>
       <c r="O382" s="15" t="inlineStr">
         <is>
           <t>CÁMARA MINIDOMO IP</t>
@@ -55790,11 +54342,7 @@
           <t>Estación Villena</t>
         </is>
       </c>
-      <c r="N383" s="15" t="inlineStr">
-        <is>
-          <t>435487</t>
-        </is>
-      </c>
+      <c r="N383" s="15" t="n"/>
       <c r="O383" s="15" t="inlineStr">
         <is>
           <t>CÁMARA MINIDOMO IP</t>
@@ -55937,11 +54485,7 @@
           <t>ATI 321.5</t>
         </is>
       </c>
-      <c r="N384" s="15" t="inlineStr">
-        <is>
-          <t>460006</t>
-        </is>
-      </c>
+      <c r="N384" s="15" t="n"/>
       <c r="O384" s="15" t="inlineStr">
         <is>
           <t>CÁMARA MINIDOMO IP</t>
@@ -56084,11 +54628,7 @@
           <t>ET Bifurcación La Oliva (Nudo I)</t>
         </is>
       </c>
-      <c r="N385" s="15" t="inlineStr">
-        <is>
-          <t>410500</t>
-        </is>
-      </c>
+      <c r="N385" s="15" t="n"/>
       <c r="O385" s="15" t="inlineStr">
         <is>
           <t>CÁMARA MINIDOMO IP</t>
@@ -56231,11 +54771,7 @@
           <t>SE 321 - SUBESTACIÓN ELÉCTRICA SAX</t>
         </is>
       </c>
-      <c r="N386" s="15" t="inlineStr">
-        <is>
-          <t>438478</t>
-        </is>
-      </c>
+      <c r="N386" s="15" t="n"/>
       <c r="O386" s="15" t="inlineStr">
         <is>
           <t>CÁMARA MINIDOMO IP</t>
@@ -56378,11 +54914,7 @@
           <t>ATI 312.2</t>
         </is>
       </c>
-      <c r="N387" s="15" t="inlineStr">
-        <is>
-          <t>355696</t>
-        </is>
-      </c>
+      <c r="N387" s="15" t="n"/>
       <c r="O387" s="15" t="inlineStr">
         <is>
           <t>CÁMARA MINIDOMO IP</t>
@@ -56525,11 +55057,7 @@
           <t>POZO BOMBAS TÚNEL</t>
         </is>
       </c>
-      <c r="N388" s="15" t="inlineStr">
-        <is>
-          <t>483956</t>
-        </is>
-      </c>
+      <c r="N388" s="15" t="n"/>
       <c r="O388" s="15" t="inlineStr">
         <is>
           <t>CÁMARA MINIDOMO IP</t>
@@ -56672,11 +55200,7 @@
           <t>ATI 312.5</t>
         </is>
       </c>
-      <c r="N389" s="15" t="inlineStr">
-        <is>
-          <t>398537</t>
-        </is>
-      </c>
+      <c r="N389" s="15" t="n"/>
       <c r="O389" s="15" t="inlineStr">
         <is>
           <t>CÁMARA MINIDOMO IP</t>
@@ -56819,11 +55343,7 @@
           <t>ATI 312.3</t>
         </is>
       </c>
-      <c r="N390" s="15" t="inlineStr">
-        <is>
-          <t>365625</t>
-        </is>
-      </c>
+      <c r="N390" s="15" t="n"/>
       <c r="O390" s="15" t="inlineStr">
         <is>
           <t>CÁMARA MINIDOMO IP</t>
@@ -56966,11 +55486,7 @@
           <t>SE 312 - SUBESTACIÓN ELÉCTRICA CAMPANARIO</t>
         </is>
       </c>
-      <c r="N391" s="15" t="inlineStr">
-        <is>
-          <t>378076</t>
-        </is>
-      </c>
+      <c r="N391" s="15" t="n"/>
       <c r="O391" s="15" t="inlineStr">
         <is>
           <t>CÁMARA MINIDOMO IP</t>
@@ -57113,11 +55629,7 @@
           <t>ET PAET Villena AV</t>
         </is>
       </c>
-      <c r="N392" s="15" t="inlineStr">
-        <is>
-          <t>435487</t>
-        </is>
-      </c>
+      <c r="N392" s="15" t="n"/>
       <c r="O392" s="15" t="inlineStr">
         <is>
           <t>CÁMARA MINIDOMO IP</t>
@@ -57260,11 +55772,7 @@
           <t>ATI 321.7</t>
         </is>
       </c>
-      <c r="N393" s="15" t="inlineStr">
-        <is>
-          <t>481640</t>
-        </is>
-      </c>
+      <c r="N393" s="15" t="n"/>
       <c r="O393" s="15" t="inlineStr">
         <is>
           <t>CÁMARA MINIDOMO IP</t>
@@ -57407,11 +55915,7 @@
           <t>ATI 311.5</t>
         </is>
       </c>
-      <c r="N394" s="15" t="inlineStr">
-        <is>
-          <t>330036</t>
-        </is>
-      </c>
+      <c r="N394" s="15" t="n"/>
       <c r="O394" s="15" t="inlineStr">
         <is>
           <t>CÁMARA MINIDOMO IP</t>
@@ -57554,11 +56058,7 @@
           <t>ET PAET Chinchilla AV</t>
         </is>
       </c>
-      <c r="N395" s="15" t="inlineStr">
-        <is>
-          <t>336566</t>
-        </is>
-      </c>
+      <c r="N395" s="15" t="n"/>
       <c r="O395" s="15" t="inlineStr">
         <is>
           <t>CÁMARA MINIDOMO IP</t>
@@ -57701,11 +56201,7 @@
           <t>Estación Villena</t>
         </is>
       </c>
-      <c r="N396" s="15" t="inlineStr">
-        <is>
-          <t>435487</t>
-        </is>
-      </c>
+      <c r="N396" s="15" t="n"/>
       <c r="O396" s="15" t="inlineStr">
         <is>
           <t>CÁMARA MINIDOMO IP</t>
@@ -57848,11 +56344,7 @@
           <t>ATF 321.1</t>
         </is>
       </c>
-      <c r="N397" s="15" t="inlineStr">
-        <is>
-          <t>405999</t>
-        </is>
-      </c>
+      <c r="N397" s="15" t="n"/>
       <c r="O397" s="15" t="inlineStr">
         <is>
           <t>CÁMARA MINIDOMO IP</t>
@@ -57995,11 +56487,7 @@
           <t>GALERÍA EVACUACIÓN DEL TÚNEL DE ACCESO ALICANTE</t>
         </is>
       </c>
-      <c r="N398" s="15" t="inlineStr">
-        <is>
-          <t>483956</t>
-        </is>
-      </c>
+      <c r="N398" s="15" t="n"/>
       <c r="O398" s="15" t="inlineStr">
         <is>
           <t>CÁMARA MINIDOMO IP</t>
@@ -58142,11 +56630,7 @@
           <t>ATI 321.3</t>
         </is>
       </c>
-      <c r="N399" s="15" t="inlineStr">
-        <is>
-          <t>429607</t>
-        </is>
-      </c>
+      <c r="N399" s="15" t="n"/>
       <c r="O399" s="15" t="inlineStr">
         <is>
           <t>CÁMARA MINIDOMO IP</t>
@@ -58289,11 +56773,7 @@
           <t>ATI 321.3</t>
         </is>
       </c>
-      <c r="N400" s="15" t="inlineStr">
-        <is>
-          <t>429607</t>
-        </is>
-      </c>
+      <c r="N400" s="15" t="n"/>
       <c r="O400" s="15" t="inlineStr">
         <is>
           <t>CÁMARA MINIDOMO IP</t>
@@ -58436,11 +56916,7 @@
           <t>GALERÍA EVACUACIÓN DEL TÚNEL DE ACCESO ALICANTE</t>
         </is>
       </c>
-      <c r="N401" s="15" t="inlineStr">
-        <is>
-          <t>483956</t>
-        </is>
-      </c>
+      <c r="N401" s="15" t="n"/>
       <c r="O401" s="15" t="inlineStr">
         <is>
           <t>CÁMARA MINIDOMO IP</t>
@@ -58583,11 +57059,7 @@
           <t>GALERÍA EVACUACIÓN DEL TÚNEL DE ACCESO ALICANTE</t>
         </is>
       </c>
-      <c r="N402" s="15" t="inlineStr">
-        <is>
-          <t>483956</t>
-        </is>
-      </c>
+      <c r="N402" s="15" t="n"/>
       <c r="O402" s="15" t="inlineStr">
         <is>
           <t>CÁMARA MINIDOMO IP</t>
@@ -58730,11 +57202,7 @@
           <t>Estación Villena</t>
         </is>
       </c>
-      <c r="N403" s="15" t="inlineStr">
-        <is>
-          <t>435487</t>
-        </is>
-      </c>
+      <c r="N403" s="15" t="n"/>
       <c r="O403" s="15" t="inlineStr">
         <is>
           <t>CÁMARA MINIDOMO IP</t>
@@ -58877,11 +57345,7 @@
           <t>ATI 321.2</t>
         </is>
       </c>
-      <c r="N404" s="15" t="inlineStr">
-        <is>
-          <t>420421</t>
-        </is>
-      </c>
+      <c r="N404" s="15" t="n"/>
       <c r="O404" s="15" t="inlineStr">
         <is>
           <t>CÁMARA MINIDOMO IP</t>
@@ -59024,11 +57488,7 @@
           <t>SE 321 - SUBESTACIÓN ELÉCTRICA SAX</t>
         </is>
       </c>
-      <c r="N405" s="15" t="inlineStr">
-        <is>
-          <t>438478</t>
-        </is>
-      </c>
+      <c r="N405" s="15" t="n"/>
       <c r="O405" s="15" t="inlineStr">
         <is>
           <t>CÁMARA MINIDOMO IP</t>
@@ -59171,11 +57631,7 @@
           <t>ATI 312.4</t>
         </is>
       </c>
-      <c r="N406" s="15" t="inlineStr">
-        <is>
-          <t>387772</t>
-        </is>
-      </c>
+      <c r="N406" s="15" t="n"/>
       <c r="O406" s="15" t="inlineStr">
         <is>
           <t>CÁMARA MINIDOMO IP</t>
@@ -59318,11 +57774,7 @@
           <t>Estación Villena</t>
         </is>
       </c>
-      <c r="N407" s="15" t="inlineStr">
-        <is>
-          <t>435487</t>
-        </is>
-      </c>
+      <c r="N407" s="15" t="n"/>
       <c r="O407" s="15" t="inlineStr">
         <is>
           <t>CÁMARA MINIDOMO IP</t>
@@ -59465,11 +57917,7 @@
           <t>ET Alacant-Terminal</t>
         </is>
       </c>
-      <c r="N408" s="15" t="inlineStr">
-        <is>
-          <t>483925</t>
-        </is>
-      </c>
+      <c r="N408" s="15" t="n"/>
       <c r="O408" s="15" t="inlineStr">
         <is>
           <t>CÁMARA MINIDOMO IP</t>
@@ -59612,11 +58060,7 @@
           <t>ATI 321.7</t>
         </is>
       </c>
-      <c r="N409" s="15" t="inlineStr">
-        <is>
-          <t>481640</t>
-        </is>
-      </c>
+      <c r="N409" s="15" t="n"/>
       <c r="O409" s="15" t="inlineStr">
         <is>
           <t>CÁMARA MINIDOMO IP</t>
@@ -59759,11 +58203,7 @@
           <t>Estación Villena</t>
         </is>
       </c>
-      <c r="N410" s="15" t="inlineStr">
-        <is>
-          <t>435487</t>
-        </is>
-      </c>
+      <c r="N410" s="15" t="n"/>
       <c r="O410" s="15" t="inlineStr">
         <is>
           <t>CÁMARA MINIDOMO IP</t>
@@ -59906,11 +58346,7 @@
           <t>ET Alacant-Terminal</t>
         </is>
       </c>
-      <c r="N411" s="15" t="inlineStr">
-        <is>
-          <t>483925</t>
-        </is>
-      </c>
+      <c r="N411" s="15" t="n"/>
       <c r="O411" s="15" t="inlineStr">
         <is>
           <t>CÁMARA MINIDOMO IP</t>
@@ -60053,11 +58489,7 @@
           <t>ATI 311.5</t>
         </is>
       </c>
-      <c r="N412" s="15" t="inlineStr">
-        <is>
-          <t>330036</t>
-        </is>
-      </c>
+      <c r="N412" s="15" t="n"/>
       <c r="O412" s="15" t="inlineStr">
         <is>
           <t>CÁMARA MINIDOMO IP</t>
@@ -60200,11 +58632,7 @@
           <t>ATF 312.1</t>
         </is>
       </c>
-      <c r="N413" s="15" t="inlineStr">
-        <is>
-          <t>342890</t>
-        </is>
-      </c>
+      <c r="N413" s="15" t="n"/>
       <c r="O413" s="15" t="inlineStr">
         <is>
           <t>CÁMARA MINIDOMO IP</t>
@@ -60347,11 +58775,7 @@
           <t>ATI 321.5</t>
         </is>
       </c>
-      <c r="N414" s="15" t="inlineStr">
-        <is>
-          <t>460006</t>
-        </is>
-      </c>
+      <c r="N414" s="15" t="n"/>
       <c r="O414" s="15" t="inlineStr">
         <is>
           <t>CÁMARA MINIDOMO IP</t>
@@ -60494,11 +58918,7 @@
           <t>ET PAET Chinchilla AV</t>
         </is>
       </c>
-      <c r="N415" s="15" t="inlineStr">
-        <is>
-          <t>336566</t>
-        </is>
-      </c>
+      <c r="N415" s="15" t="n"/>
       <c r="O415" s="15" t="inlineStr">
         <is>
           <t>CÁMARA MINIDOMO IP</t>
@@ -60641,11 +59061,7 @@
           <t>ATI 312.3</t>
         </is>
       </c>
-      <c r="N416" s="15" t="inlineStr">
-        <is>
-          <t>365625</t>
-        </is>
-      </c>
+      <c r="N416" s="15" t="n"/>
       <c r="O416" s="15" t="inlineStr">
         <is>
           <t>CÁMARA MINIDOMO IP</t>
@@ -60788,11 +59204,7 @@
           <t>Estación Villena</t>
         </is>
       </c>
-      <c r="N417" s="15" t="inlineStr">
-        <is>
-          <t>435487</t>
-        </is>
-      </c>
+      <c r="N417" s="15" t="n"/>
       <c r="O417" s="15" t="inlineStr">
         <is>
           <t>CÁMARA MINIDOMO IP</t>
@@ -60935,11 +59347,7 @@
           <t>ET PAET Chinchilla AV</t>
         </is>
       </c>
-      <c r="N418" s="15" t="inlineStr">
-        <is>
-          <t>336566</t>
-        </is>
-      </c>
+      <c r="N418" s="15" t="n"/>
       <c r="O418" s="15" t="inlineStr">
         <is>
           <t>CÁMARA MINIDOMO IP</t>
@@ -61082,11 +59490,7 @@
           <t>Estación Villena</t>
         </is>
       </c>
-      <c r="N419" s="15" t="inlineStr">
-        <is>
-          <t>435487</t>
-        </is>
-      </c>
+      <c r="N419" s="15" t="n"/>
       <c r="O419" s="15" t="inlineStr">
         <is>
           <t>CÁMARA MINIDOMO IP</t>
@@ -61229,11 +59633,7 @@
           <t>ATI 321.6</t>
         </is>
       </c>
-      <c r="N420" s="15" t="inlineStr">
-        <is>
-          <t>474060</t>
-        </is>
-      </c>
+      <c r="N420" s="15" t="n"/>
       <c r="O420" s="15" t="inlineStr">
         <is>
           <t>CÁMARA MINIDOMO IP</t>
@@ -61376,11 +59776,7 @@
           <t>ET Alacant-Terminal</t>
         </is>
       </c>
-      <c r="N421" s="15" t="inlineStr">
-        <is>
-          <t>483925</t>
-        </is>
-      </c>
+      <c r="N421" s="15" t="n"/>
       <c r="O421" s="15" t="inlineStr">
         <is>
           <t>CÁMARA MINIDOMO IP</t>
@@ -61523,11 +59919,7 @@
           <t>ATI 312.4</t>
         </is>
       </c>
-      <c r="N422" s="15" t="inlineStr">
-        <is>
-          <t>387772</t>
-        </is>
-      </c>
+      <c r="N422" s="15" t="n"/>
       <c r="O422" s="15" t="inlineStr">
         <is>
           <t>CÁMARA MINIDOMO IP</t>
@@ -61670,11 +60062,7 @@
           <t>ATI 321.4</t>
         </is>
       </c>
-      <c r="N423" s="15" t="inlineStr">
-        <is>
-          <t>450660</t>
-        </is>
-      </c>
+      <c r="N423" s="15" t="n"/>
       <c r="O423" s="15" t="inlineStr">
         <is>
           <t>CÁMARA MINIDOMO IP</t>
@@ -61817,11 +60205,7 @@
           <t>ET PAET BONETE AV (MTO UTE)</t>
         </is>
       </c>
-      <c r="N424" s="15" t="inlineStr">
-        <is>
-          <t>373493</t>
-        </is>
-      </c>
+      <c r="N424" s="15" t="n"/>
       <c r="O424" s="15" t="inlineStr">
         <is>
           <t>CÁMARA MINIDOMO IP</t>
@@ -61964,11 +60348,7 @@
           <t>ATF 321.1</t>
         </is>
       </c>
-      <c r="N425" s="15" t="inlineStr">
-        <is>
-          <t>405999</t>
-        </is>
-      </c>
+      <c r="N425" s="15" t="n"/>
       <c r="O425" s="15" t="inlineStr">
         <is>
           <t>CÁMARA MINIDOMO IP</t>
@@ -62111,11 +60491,7 @@
           <t>ET Bifurcación La Oliva (Nudo I)</t>
         </is>
       </c>
-      <c r="N426" s="15" t="inlineStr">
-        <is>
-          <t>410500</t>
-        </is>
-      </c>
+      <c r="N426" s="15" t="n"/>
       <c r="O426" s="15" t="inlineStr">
         <is>
           <t>CÁMARA MINIDOMO IP</t>
@@ -62258,11 +60634,7 @@
           <t>ET PAET BONETE AV (MTO UTE)</t>
         </is>
       </c>
-      <c r="N427" s="15" t="inlineStr">
-        <is>
-          <t>373493</t>
-        </is>
-      </c>
+      <c r="N427" s="15" t="n"/>
       <c r="O427" s="15" t="inlineStr">
         <is>
           <t>CÁMARA MINIDOMO IP</t>
@@ -62405,11 +60777,7 @@
           <t>BASE DE MANTENIMIENTO MONFORTE DEL CID (NODO-1)</t>
         </is>
       </c>
-      <c r="N428" s="15" t="inlineStr">
-        <is>
-          <t>465134</t>
-        </is>
-      </c>
+      <c r="N428" s="15" t="n"/>
       <c r="O428" s="15" t="inlineStr">
         <is>
           <t>CÁMARA MINIDOMO IP</t>
@@ -62552,11 +60920,7 @@
           <t>BASE DE MANTENIMIENTO MONFORTE DEL CID (NODO-1)</t>
         </is>
       </c>
-      <c r="N429" s="15" t="inlineStr">
-        <is>
-          <t>465134</t>
-        </is>
-      </c>
+      <c r="N429" s="15" t="n"/>
       <c r="O429" s="15" t="inlineStr">
         <is>
           <t>CÁMARA MINIDOMO IP</t>
@@ -62699,11 +61063,7 @@
           <t>ET PAET BONETE AV (MTO UTE)</t>
         </is>
       </c>
-      <c r="N430" s="15" t="inlineStr">
-        <is>
-          <t>373493</t>
-        </is>
-      </c>
+      <c r="N430" s="15" t="n"/>
       <c r="O430" s="15" t="inlineStr">
         <is>
           <t>CÁMARA MINIDOMO IP</t>
@@ -62846,11 +61206,7 @@
           <t>ET PAET MONFORTE DEL CID AV (MTO UTE)</t>
         </is>
       </c>
-      <c r="N431" s="15" t="inlineStr">
-        <is>
-          <t>464685</t>
-        </is>
-      </c>
+      <c r="N431" s="15" t="n"/>
       <c r="O431" s="15" t="inlineStr">
         <is>
           <t>CÁMARA MINIDOMO IP</t>
@@ -62993,11 +61349,7 @@
           <t>BASE DE MANTENIMIENTO MONFORTE DEL CID (NODO-1)</t>
         </is>
       </c>
-      <c r="N432" s="15" t="inlineStr">
-        <is>
-          <t>465134</t>
-        </is>
-      </c>
+      <c r="N432" s="15" t="n"/>
       <c r="O432" s="15" t="inlineStr">
         <is>
           <t>CÁMARA MINIDOMO IP</t>
@@ -63140,11 +61492,7 @@
           <t>ET PAET MONFORTE DEL CID AV (MTO UTE)</t>
         </is>
       </c>
-      <c r="N433" s="15" t="inlineStr">
-        <is>
-          <t>464685</t>
-        </is>
-      </c>
+      <c r="N433" s="15" t="n"/>
       <c r="O433" s="15" t="inlineStr">
         <is>
           <t>CÁMARA MINIDOMO IP</t>
@@ -63287,11 +61635,7 @@
           <t>BASE DE MANTENIMIENTO MONFORTE DEL CID (NODO-1)</t>
         </is>
       </c>
-      <c r="N434" s="15" t="inlineStr">
-        <is>
-          <t>465134</t>
-        </is>
-      </c>
+      <c r="N434" s="15" t="n"/>
       <c r="O434" s="15" t="inlineStr">
         <is>
           <t>CÁMARA MINIDOMO IP</t>
@@ -63434,11 +61778,7 @@
           <t>ET PAET BONETE AV (MTO UTE)</t>
         </is>
       </c>
-      <c r="N435" s="15" t="inlineStr">
-        <is>
-          <t>373493</t>
-        </is>
-      </c>
+      <c r="N435" s="15" t="n"/>
       <c r="O435" s="15" t="inlineStr">
         <is>
           <t>CÁMARA MINIDOMO IP</t>
@@ -63581,11 +61921,7 @@
           <t>BASE DE MANTENIMIENTO MONFORTE DEL CID (NODO-1)</t>
         </is>
       </c>
-      <c r="N436" s="15" t="inlineStr">
-        <is>
-          <t>465134</t>
-        </is>
-      </c>
+      <c r="N436" s="15" t="n"/>
       <c r="O436" s="15" t="inlineStr">
         <is>
           <t>CÁMARA MINIDOMO IP</t>
@@ -63728,11 +62064,7 @@
           <t>ET PAET MONFORTE DEL CID AV (MTO UTE)</t>
         </is>
       </c>
-      <c r="N437" s="15" t="inlineStr">
-        <is>
-          <t>464685</t>
-        </is>
-      </c>
+      <c r="N437" s="15" t="n"/>
       <c r="O437" s="15" t="inlineStr">
         <is>
           <t>CÁMARA MINIDOMO IP</t>
@@ -63875,11 +62207,7 @@
           <t>Estación Villena</t>
         </is>
       </c>
-      <c r="N438" s="15" t="inlineStr">
-        <is>
-          <t>435487</t>
-        </is>
-      </c>
+      <c r="N438" s="15" t="n"/>
       <c r="O438" s="15" t="inlineStr">
         <is>
           <t>CÁMARA MINIDOMO IP</t>
@@ -64022,11 +62350,7 @@
           <t>ET PAET BONETE AV (MTO UTE)</t>
         </is>
       </c>
-      <c r="N439" s="15" t="inlineStr">
-        <is>
-          <t>373493</t>
-        </is>
-      </c>
+      <c r="N439" s="15" t="n"/>
       <c r="O439" s="15" t="inlineStr">
         <is>
           <t>CÁMARA MINIDOMO IP</t>
@@ -64169,11 +62493,7 @@
           <t>ET PAET MONFORTE DEL CID AV (MTO UTE)</t>
         </is>
       </c>
-      <c r="N440" s="15" t="inlineStr">
-        <is>
-          <t>464685</t>
-        </is>
-      </c>
+      <c r="N440" s="15" t="n"/>
       <c r="O440" s="15" t="inlineStr">
         <is>
           <t>CÁMARA MINIDOMO IP</t>
@@ -64316,11 +62636,7 @@
           <t>ET PAET BONETE AV (MTO UTE)</t>
         </is>
       </c>
-      <c r="N441" s="15" t="inlineStr">
-        <is>
-          <t>373493</t>
-        </is>
-      </c>
+      <c r="N441" s="15" t="n"/>
       <c r="O441" s="15" t="inlineStr">
         <is>
           <t>CÁMARA MINIDOMO IP</t>
@@ -64463,11 +62779,7 @@
           <t>ATI 321.4</t>
         </is>
       </c>
-      <c r="N442" s="15" t="inlineStr">
-        <is>
-          <t>450660</t>
-        </is>
-      </c>
+      <c r="N442" s="15" t="n"/>
       <c r="O442" s="15" t="inlineStr">
         <is>
           <t>CÁMARA FIJA IP</t>
@@ -64610,11 +62922,7 @@
           <t>PS 468,4 a</t>
         </is>
       </c>
-      <c r="N443" s="15" t="inlineStr">
-        <is>
-          <t>468417</t>
-        </is>
-      </c>
+      <c r="N443" s="15" t="n"/>
       <c r="O443" s="15" t="inlineStr">
         <is>
           <t>CÁMARA FIJA IP</t>
@@ -64757,11 +63065,7 @@
           <t>PS 483,5 a</t>
         </is>
       </c>
-      <c r="N444" s="15" t="inlineStr">
-        <is>
-          <t>483564</t>
-        </is>
-      </c>
+      <c r="N444" s="15" t="n"/>
       <c r="O444" s="15" t="inlineStr">
         <is>
           <t>CÁMARA FIJA IP</t>
@@ -64904,11 +63208,7 @@
           <t>PS 322,3a (PS 322,6a)</t>
         </is>
       </c>
-      <c r="N445" s="15" t="inlineStr">
-        <is>
-          <t>322398</t>
-        </is>
-      </c>
+      <c r="N445" s="15" t="n"/>
       <c r="O445" s="15" t="inlineStr">
         <is>
           <t>CÁMARA FIJA IP</t>
@@ -65051,11 +63351,7 @@
           <t>PS 342,7 a</t>
         </is>
       </c>
-      <c r="N446" s="15" t="inlineStr">
-        <is>
-          <t>342773</t>
-        </is>
-      </c>
+      <c r="N446" s="15" t="n"/>
       <c r="O446" s="15" t="inlineStr">
         <is>
           <t>CÁMARA FIJA IP</t>
@@ -65198,11 +63494,7 @@
           <t>PS 376,9 a</t>
         </is>
       </c>
-      <c r="N447" s="15" t="inlineStr">
-        <is>
-          <t>376992</t>
-        </is>
-      </c>
+      <c r="N447" s="15" t="n"/>
       <c r="O447" s="15" t="inlineStr">
         <is>
           <t>CÁMARA FIJA IP</t>
@@ -65345,11 +63637,7 @@
           <t>PS 361,6 a</t>
         </is>
       </c>
-      <c r="N448" s="15" t="inlineStr">
-        <is>
-          <t>361619</t>
-        </is>
-      </c>
+      <c r="N448" s="15" t="n"/>
       <c r="O448" s="15" t="inlineStr">
         <is>
           <t>CÁMARA FIJA IP</t>
@@ -65492,11 +63780,7 @@
           <t>VIADUCTO SOBRE RÍO VINALOPÓ</t>
         </is>
       </c>
-      <c r="N449" s="15" t="inlineStr">
-        <is>
-          <t>454684</t>
-        </is>
-      </c>
+      <c r="N449" s="15" t="n"/>
       <c r="O449" s="15" t="inlineStr">
         <is>
           <t>CÁMARA FIJA IP</t>
@@ -65639,11 +63923,7 @@
           <t>ATI 321.6</t>
         </is>
       </c>
-      <c r="N450" s="15" t="inlineStr">
-        <is>
-          <t>474060</t>
-        </is>
-      </c>
+      <c r="N450" s="15" t="n"/>
       <c r="O450" s="15" t="inlineStr">
         <is>
           <t>CÁMARA FIJA IP</t>
@@ -65786,11 +64066,7 @@
           <t>ATI 321.3</t>
         </is>
       </c>
-      <c r="N451" s="15" t="inlineStr">
-        <is>
-          <t>429607</t>
-        </is>
-      </c>
+      <c r="N451" s="15" t="n"/>
       <c r="O451" s="15" t="inlineStr">
         <is>
           <t>CÁMARA FIJA IP</t>
@@ -65933,11 +64209,7 @@
           <t>ET PAET Villena AV</t>
         </is>
       </c>
-      <c r="N452" s="15" t="inlineStr">
-        <is>
-          <t>435487</t>
-        </is>
-      </c>
+      <c r="N452" s="15" t="n"/>
       <c r="O452" s="15" t="inlineStr">
         <is>
           <t>CÁMARA FIJA IP</t>
@@ -66080,11 +64352,7 @@
           <t>PÉRGOLA SOBRE VÍA ALICANTE-VILLENA</t>
         </is>
       </c>
-      <c r="N453" s="15" t="inlineStr">
-        <is>
-          <t>482404</t>
-        </is>
-      </c>
+      <c r="N453" s="15" t="n"/>
       <c r="O453" s="15" t="inlineStr">
         <is>
           <t>CÁMARA FIJA IP</t>
@@ -66227,11 +64495,7 @@
           <t>PS 426,2 a</t>
         </is>
       </c>
-      <c r="N454" s="15" t="inlineStr">
-        <is>
-          <t>426243</t>
-        </is>
-      </c>
+      <c r="N454" s="15" t="n"/>
       <c r="O454" s="15" t="inlineStr">
         <is>
           <t>CÁMARA FIJA IP</t>
@@ -66374,11 +64638,7 @@
           <t>PS 478,1 a</t>
         </is>
       </c>
-      <c r="N455" s="15" t="inlineStr">
-        <is>
-          <t>478169</t>
-        </is>
-      </c>
+      <c r="N455" s="15" t="n"/>
       <c r="O455" s="15" t="inlineStr">
         <is>
           <t>CÁMARA FIJA IP</t>
@@ -66521,11 +64781,7 @@
           <t>PS 401,5 a</t>
         </is>
       </c>
-      <c r="N456" s="15" t="inlineStr">
-        <is>
-          <t>401522</t>
-        </is>
-      </c>
+      <c r="N456" s="15" t="n"/>
       <c r="O456" s="15" t="inlineStr">
         <is>
           <t>CÁMARA FIJA IP</t>
@@ -66668,11 +64924,7 @@
           <t>PS 385,4a (PS 385,3 a)</t>
         </is>
       </c>
-      <c r="N457" s="15" t="inlineStr">
-        <is>
-          <t>385406</t>
-        </is>
-      </c>
+      <c r="N457" s="15" t="n"/>
       <c r="O457" s="15" t="inlineStr">
         <is>
           <t>CÁMARA FIJA IP</t>
@@ -66815,11 +65067,7 @@
           <t>ET Alacant-Terminal</t>
         </is>
       </c>
-      <c r="N458" s="15" t="inlineStr">
-        <is>
-          <t>483925</t>
-        </is>
-      </c>
+      <c r="N458" s="15" t="n"/>
       <c r="O458" s="15" t="inlineStr">
         <is>
           <t>CÁMARA FIJA IP</t>
@@ -66962,11 +65210,7 @@
           <t>Estación Villena</t>
         </is>
       </c>
-      <c r="N459" s="15" t="inlineStr">
-        <is>
-          <t>435487</t>
-        </is>
-      </c>
+      <c r="N459" s="15" t="n"/>
       <c r="O459" s="15" t="inlineStr">
         <is>
           <t>CÁMARA FIJA IP</t>
@@ -67109,11 +65353,7 @@
           <t>PS 431,1 a</t>
         </is>
       </c>
-      <c r="N460" s="15" t="inlineStr">
-        <is>
-          <t>431159</t>
-        </is>
-      </c>
+      <c r="N460" s="15" t="n"/>
       <c r="O460" s="15" t="inlineStr">
         <is>
           <t>CÁMARA FIJA IP</t>
@@ -67256,11 +65496,7 @@
           <t>PS 328,8 a A-31 (PS UNIDO AL PS-328,883)</t>
         </is>
       </c>
-      <c r="N461" s="15" t="inlineStr">
-        <is>
-          <t>328815</t>
-        </is>
-      </c>
+      <c r="N461" s="15" t="n"/>
       <c r="O461" s="15" t="inlineStr">
         <is>
           <t>CÁMARA FIJA IP</t>
@@ -67403,11 +65639,7 @@
           <t>PS 376,0 a</t>
         </is>
       </c>
-      <c r="N462" s="15" t="inlineStr">
-        <is>
-          <t>376072</t>
-        </is>
-      </c>
+      <c r="N462" s="15" t="n"/>
       <c r="O462" s="15" t="inlineStr">
         <is>
           <t>CÁMARA FIJA IP</t>
@@ -67550,11 +65782,7 @@
           <t>ET PAET Villena AV</t>
         </is>
       </c>
-      <c r="N463" s="15" t="inlineStr">
-        <is>
-          <t>435487</t>
-        </is>
-      </c>
+      <c r="N463" s="15" t="n"/>
       <c r="O463" s="15" t="inlineStr">
         <is>
           <t>CÁMARA FIJA IP</t>
@@ -67697,11 +65925,7 @@
           <t>PS 370,0 a</t>
         </is>
       </c>
-      <c r="N464" s="15" t="inlineStr">
-        <is>
-          <t>370069</t>
-        </is>
-      </c>
+      <c r="N464" s="15" t="n"/>
       <c r="O464" s="15" t="inlineStr">
         <is>
           <t>CÁMARA FIJA IP</t>
@@ -67844,11 +66068,7 @@
           <t>PS 368,9 a</t>
         </is>
       </c>
-      <c r="N465" s="15" t="inlineStr">
-        <is>
-          <t>368928</t>
-        </is>
-      </c>
+      <c r="N465" s="15" t="n"/>
       <c r="O465" s="15" t="inlineStr">
         <is>
           <t>CÁMARA FIJA IP</t>
@@ -67991,11 +66211,7 @@
           <t>PS 350,6 a</t>
         </is>
       </c>
-      <c r="N466" s="15" t="inlineStr">
-        <is>
-          <t>350643</t>
-        </is>
-      </c>
+      <c r="N466" s="15" t="n"/>
       <c r="O466" s="15" t="inlineStr">
         <is>
           <t>CÁMARA FIJA IP</t>
@@ -68138,11 +66354,7 @@
           <t>PS 367,2 a</t>
         </is>
       </c>
-      <c r="N467" s="15" t="inlineStr">
-        <is>
-          <t>367224</t>
-        </is>
-      </c>
+      <c r="N467" s="15" t="n"/>
       <c r="O467" s="15" t="inlineStr">
         <is>
           <t>CÁMARA FIJA IP</t>
@@ -68374,11 +66586,7 @@
           <t>PS PÉRGOLA Cajón A-31 - TM344,3 a - TL344,5 a</t>
         </is>
       </c>
-      <c r="N469" s="15" t="inlineStr">
-        <is>
-          <t>344398</t>
-        </is>
-      </c>
+      <c r="N469" s="15" t="n"/>
       <c r="O469" s="15" t="inlineStr">
         <is>
           <t>CÁMARA FIJA IP</t>
@@ -68521,11 +66729,7 @@
           <t>ATI 321.2</t>
         </is>
       </c>
-      <c r="N470" s="15" t="inlineStr">
-        <is>
-          <t>420421</t>
-        </is>
-      </c>
+      <c r="N470" s="15" t="n"/>
       <c r="O470" s="15" t="inlineStr">
         <is>
           <t>CÁMARA FIJA IP</t>
@@ -68668,11 +66872,7 @@
           <t>ATI 321.5</t>
         </is>
       </c>
-      <c r="N471" s="15" t="inlineStr">
-        <is>
-          <t>460006</t>
-        </is>
-      </c>
+      <c r="N471" s="15" t="n"/>
       <c r="O471" s="15" t="inlineStr">
         <is>
           <t>CÁMARA FIJA IP</t>
@@ -68815,11 +67015,7 @@
           <t>ET Alacant-Terminal</t>
         </is>
       </c>
-      <c r="N472" s="15" t="inlineStr">
-        <is>
-          <t>483925</t>
-        </is>
-      </c>
+      <c r="N472" s="15" t="n"/>
       <c r="O472" s="15" t="inlineStr">
         <is>
           <t>CÁMARA FIJA IP</t>
@@ -68962,11 +67158,7 @@
           <t>PCA Alcoraya</t>
         </is>
       </c>
-      <c r="N473" s="15" t="inlineStr">
-        <is>
-          <t>476931</t>
-        </is>
-      </c>
+      <c r="N473" s="15" t="n"/>
       <c r="O473" s="15" t="inlineStr">
         <is>
           <t>CÁMARA FIJA IP</t>
@@ -69109,11 +67301,7 @@
           <t>PS 372,2 a</t>
         </is>
       </c>
-      <c r="N474" s="15" t="inlineStr">
-        <is>
-          <t>372221</t>
-        </is>
-      </c>
+      <c r="N474" s="15" t="n"/>
       <c r="O474" s="15" t="inlineStr">
         <is>
           <t>CÁMARA FIJA IP</t>
@@ -69256,11 +67444,7 @@
           <t>PS 328,6 a</t>
         </is>
       </c>
-      <c r="N475" s="15" t="inlineStr">
-        <is>
-          <t>328611</t>
-        </is>
-      </c>
+      <c r="N475" s="15" t="n"/>
       <c r="O475" s="15" t="inlineStr">
         <is>
           <t>CÁMARA FIJA IP</t>
@@ -69403,11 +67587,7 @@
           <t>PS 428,7 a</t>
         </is>
       </c>
-      <c r="N476" s="15" t="inlineStr">
-        <is>
-          <t>428763</t>
-        </is>
-      </c>
+      <c r="N476" s="15" t="n"/>
       <c r="O476" s="15" t="inlineStr">
         <is>
           <t>CÁMARA FIJA IP</t>
@@ -69550,11 +67730,7 @@
           <t>PS 328,9 a A-31 (PS UNIDO AL PS-328,832)</t>
         </is>
       </c>
-      <c r="N477" s="15" t="inlineStr">
-        <is>
-          <t>328866</t>
-        </is>
-      </c>
+      <c r="N477" s="15" t="n"/>
       <c r="O477" s="15" t="inlineStr">
         <is>
           <t>CÁMARA FIJA IP</t>
@@ -69697,11 +67873,7 @@
           <t>ET PAET Chinchilla AV</t>
         </is>
       </c>
-      <c r="N478" s="15" t="inlineStr">
-        <is>
-          <t>336566</t>
-        </is>
-      </c>
+      <c r="N478" s="15" t="n"/>
       <c r="O478" s="15" t="inlineStr">
         <is>
           <t>CÁMARA FIJA IP</t>
@@ -69844,11 +68016,7 @@
           <t>VIADUCTO SOBRE A-31</t>
         </is>
       </c>
-      <c r="N479" s="15" t="inlineStr">
-        <is>
-          <t>419205</t>
-        </is>
-      </c>
+      <c r="N479" s="15" t="n"/>
       <c r="O479" s="15" t="inlineStr">
         <is>
           <t>CÁMARA FIJA IP</t>
@@ -71383,11 +69551,7 @@
           <t>BASE DE MANTENIMIENTO MONFORTE DEL CID (NODO-7 NAV</t>
         </is>
       </c>
-      <c r="N496" s="15" t="inlineStr">
-        <is>
-          <t>465134</t>
-        </is>
-      </c>
+      <c r="N496" s="15" t="n"/>
       <c r="O496" s="15" t="inlineStr">
         <is>
           <t>CÁMARA DOMO IP</t>
@@ -71530,11 +69694,7 @@
           <t>ET PAET BONETE AV (MTO UTE)</t>
         </is>
       </c>
-      <c r="N497" s="15" t="inlineStr">
-        <is>
-          <t>373493</t>
-        </is>
-      </c>
+      <c r="N497" s="15" t="n"/>
       <c r="O497" s="15" t="inlineStr">
         <is>
           <t>CÁMARA DOMO IP</t>
@@ -71677,11 +69837,7 @@
           <t>ATF 321.1</t>
         </is>
       </c>
-      <c r="N498" s="15" t="inlineStr">
-        <is>
-          <t>405999</t>
-        </is>
-      </c>
+      <c r="N498" s="15" t="n"/>
       <c r="O498" s="15" t="inlineStr">
         <is>
           <t>CÁMARA DOMO IP</t>
@@ -71824,11 +69980,7 @@
           <t>BASE DE MANTENIMIENTO MONFORTE DEL CID (NODO-7 NAV</t>
         </is>
       </c>
-      <c r="N499" s="15" t="inlineStr">
-        <is>
-          <t>465134</t>
-        </is>
-      </c>
+      <c r="N499" s="15" t="n"/>
       <c r="O499" s="15" t="inlineStr">
         <is>
           <t>CÁMARA DOMO IP</t>
@@ -71971,11 +70123,7 @@
           <t>BTS 15B</t>
         </is>
       </c>
-      <c r="N500" s="15" t="inlineStr">
-        <is>
-          <t>440640</t>
-        </is>
-      </c>
+      <c r="N500" s="15" t="n"/>
       <c r="O500" s="15" t="inlineStr">
         <is>
           <t>CÁMARA DOMO IP</t>
@@ -72118,11 +70266,7 @@
           <t>BASE DE MANTENIMIENTO MONFORTE DEL CID (NODO-1)</t>
         </is>
       </c>
-      <c r="N501" s="15" t="inlineStr">
-        <is>
-          <t>465134</t>
-        </is>
-      </c>
+      <c r="N501" s="15" t="n"/>
       <c r="O501" s="15" t="inlineStr">
         <is>
           <t>CÁMARA DOMO IP</t>
@@ -72265,11 +70409,7 @@
           <t>BASE DE MANTENIMIENTO MONFORTE DEL CID (NODO-1)</t>
         </is>
       </c>
-      <c r="N502" s="15" t="inlineStr">
-        <is>
-          <t>465134</t>
-        </is>
-      </c>
+      <c r="N502" s="15" t="n"/>
       <c r="O502" s="15" t="inlineStr">
         <is>
           <t>CÁMARA DOMO IP</t>
@@ -72412,11 +70552,7 @@
           <t>ATI 312.4</t>
         </is>
       </c>
-      <c r="N503" s="15" t="inlineStr">
-        <is>
-          <t>387772</t>
-        </is>
-      </c>
+      <c r="N503" s="15" t="n"/>
       <c r="O503" s="15" t="inlineStr">
         <is>
           <t>CÁMARA DOMO IP</t>
@@ -72559,11 +70695,7 @@
           <t>BASE DE MANTENIMIENTO MONFORTE DEL CID (NODO-2)</t>
         </is>
       </c>
-      <c r="N504" s="15" t="inlineStr">
-        <is>
-          <t>465134</t>
-        </is>
-      </c>
+      <c r="N504" s="15" t="n"/>
       <c r="O504" s="15" t="inlineStr">
         <is>
           <t>CÁMARA DOMO IP</t>
@@ -72706,11 +70838,7 @@
           <t>ET PAET MONFORTE DEL CID AV (MTO UTE)</t>
         </is>
       </c>
-      <c r="N505" s="15" t="inlineStr">
-        <is>
-          <t>464685</t>
-        </is>
-      </c>
+      <c r="N505" s="15" t="n"/>
       <c r="O505" s="15" t="inlineStr">
         <is>
           <t>CÁMARA DOMO IP</t>
